--- a/outputs/env-evolution-research/benchmark_landscape.xlsx
+++ b/outputs/env-evolution-research/benchmark_landscape.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Benchmark landscape" sheetId="1" r:id="R696c300632fd485c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methods" sheetId="2" r:id="R4c55f40bb4424bd6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="3" r:id="R99dd05ced25d4370"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Benchmark landscape" sheetId="1" r:id="R61aa6a66225d4f38"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methods" sheetId="2" r:id="R1fd9a52e6733437d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="3" r:id="R67e2b9f1742e44dc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -15,7 +15,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="12">
+  <x:fonts count="15">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -84,8 +84,24 @@
       <x:color rgb="FF475569"/>
       <x:name val="Arial"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="15"/>
+      <x:color rgb="FF1F2937"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:sz val="8"/>
+      <x:color rgb="FF0563C1"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:sz val="9"/>
+      <x:color rgb="FF334155"/>
+      <x:name val="Arial"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="8">
+  <x:fills count="10">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -120,6 +136,16 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF44546A"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -202,7 +228,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="92">
+  <x:cellXfs count="114">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -407,11 +433,65 @@
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="6">
+  <x:dxfs count="12">
     <x:dxf>
       <x:font>
         <x:b/>
@@ -442,6 +522,70 @@
       <x:fill>
         <x:patternFill>
           <x:bgColor rgb="FFE7E6E6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FFC2410C"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFCE8D8"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF92400E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFEF3C7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF4B5563"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFE5E7EB"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FFC2410C"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFCE8D8"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF92400E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFEF3C7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF4B5563"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFE5E7EB"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -482,27 +626,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BenchmarkRoadmapTable" displayName="BenchmarkRoadmapTable" ref="A7:S35" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="19">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="BenchmarkResearchGuideTable" displayName="BenchmarkResearchGuideTable" ref="A7:M35" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="13">
     <x:tableColumn id="1" name="Priority"/>
-    <x:tableColumn id="2" name="Score"/>
-    <x:tableColumn id="3" name="Benchmark / testbed"/>
-    <x:tableColumn id="4" name="Roadmap role"/>
-    <x:tableColumn id="5" name="Current project anchor"/>
-    <x:tableColumn id="6" name="Domain"/>
-    <x:tableColumn id="7" name="Interface"/>
-    <x:tableColumn id="8" name="First executable slice"/>
-    <x:tableColumn id="9" name="Native verifier"/>
-    <x:tableColumn id="10" name="Reset / snapshot"/>
-    <x:tableColumn id="11" name="Adapter"/>
-    <x:tableColumn id="12" name="Verifier"/>
-    <x:tableColumn id="13" name="Reset"/>
-    <x:tableColumn id="14" name="Six phases"/>
-    <x:tableColumn id="15" name="Diagnostics"/>
-    <x:tableColumn id="16" name="Run cost"/>
-    <x:tableColumn id="17" name="Transfer"/>
-    <x:tableColumn id="18" name="Next action / reason"/>
-    <x:tableColumn id="19" name="Source ID"/>
+    <x:tableColumn id="2" name="Benchmark / testbed"/>
+    <x:tableColumn id="3" name="Detailed introduction"/>
+    <x:tableColumn id="4" name="Environment and state"/>
+    <x:tableColumn id="5" name="Agent interface / action space"/>
+    <x:tableColumn id="6" name="Representative task example"/>
+    <x:tableColumn id="7" name="Native verifier / success condition"/>
+    <x:tableColumn id="8" name="Suitable environment changes"/>
+    <x:tableColumn id="9" name="Relation to current project"/>
+    <x:tableColumn id="10" name="Paper / project link"/>
+    <x:tableColumn id="11" name="Code / data link"/>
+    <x:tableColumn id="12" name="Research role"/>
+    <x:tableColumn id="13" name="Source ID"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -736,17 +874,17 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="10" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="8" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="29" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="17" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="19" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="35" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="28" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="23" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="10" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="10" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="26" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="46" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="42" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="36" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="43" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="39" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="37" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="43" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="38" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="51" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="26" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="10" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="10" hidden="0" customWidth="1"/>
     <x:col min="15" max="15" width="10" hidden="0" customWidth="1"/>
@@ -757,27 +895,27 @@
   </x:cols>
   <x:sheetData>
     <x:row r="2">
-      <x:c r="A2" s="67" t="str">
-        <x:v>Env-Agent-RSI benchmark roadmap</x:v>
-      </x:c>
-      <x:c r="B2" s="67"/>
-      <x:c r="C2" s="67"/>
-      <x:c r="D2" s="67"/>
-      <x:c r="E2" s="67"/>
-      <x:c r="F2" s="67"/>
-      <x:c r="G2" s="67"/>
-      <x:c r="H2" s="67"/>
-      <x:c r="I2" s="67"/>
-      <x:c r="J2" s="67"/>
-      <x:c r="K2" s="67"/>
-      <x:c r="L2" s="67"/>
-      <x:c r="M2" s="67"/>
-      <x:c r="N2" s="67"/>
-      <x:c r="O2" s="67"/>
-      <x:c r="P2" s="67"/>
-      <x:c r="Q2" s="67"/>
-      <x:c r="R2" s="67"/>
-      <x:c r="S2" s="67"/>
+      <x:c r="A2" s="92" t="str">
+        <x:v>Env-Agent-RSI benchmark research guide</x:v>
+      </x:c>
+      <x:c r="B2" s="92"/>
+      <x:c r="C2" s="92"/>
+      <x:c r="D2" s="92"/>
+      <x:c r="E2" s="92"/>
+      <x:c r="F2" s="92"/>
+      <x:c r="G2" s="92"/>
+      <x:c r="H2" s="92"/>
+      <x:c r="I2" s="92"/>
+      <x:c r="J2" s="92"/>
+      <x:c r="K2" s="92"/>
+      <x:c r="L2" s="92"/>
+      <x:c r="M2" s="92"/>
+      <x:c r="N2"/>
+      <x:c r="O2"/>
+      <x:c r="P2"/>
+      <x:c r="Q2"/>
+      <x:c r="R2"/>
+      <x:c r="S2"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="68"/>
@@ -793,1846 +931,1458 @@
       <x:c r="K3" s="68"/>
       <x:c r="L3" s="68"/>
       <x:c r="M3" s="68"/>
-      <x:c r="N3" s="68"/>
-      <x:c r="O3" s="68"/>
-      <x:c r="P3" s="68"/>
-      <x:c r="Q3" s="68"/>
-      <x:c r="R3" s="68"/>
-      <x:c r="S3" s="68"/>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="79" t="str">
+      <x:c r="N3"/>
+      <x:c r="O3"/>
+      <x:c r="P3"/>
+      <x:c r="Q3"/>
+      <x:c r="R3"/>
+      <x:c r="S3"/>
+    </x:row>
+    <x:row r="4" ht="28" customHeight="1">
+      <x:c r="A4" s="104" t="str">
         <x:v>P0 count</x:v>
       </x:c>
-      <x:c r="B4" s="79" t="n">
+      <x:c r="B4" s="105" t="n">
         <x:f>COUNTIF(A8:A35,"P0")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C4" s="79" t="str">
+      <x:c r="C4" s="106" t="str">
         <x:v>P1 count</x:v>
       </x:c>
-      <x:c r="D4" s="79" t="n">
+      <x:c r="D4" s="105" t="n">
         <x:f>COUNTIF(A8:A35,"P1")</x:f>
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="E4" s="79" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E4" s="106" t="str">
         <x:v>P2 count</x:v>
       </x:c>
-      <x:c r="F4" s="79" t="n">
+      <x:c r="F4" s="105" t="n">
         <x:f>COUNTIF(A8:A35,"P2")</x:f>
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G4"/>
       <x:c r="H4" s="79" t="str">
-        <x:v>Scoring</x:v>
-      </x:c>
-      <x:c r="I4" s="80" t="str">
-        <x:v>七项各 0–2：adapter 复用、verifier、reset、六阶段、诊断信号、运行成本、场景迁移。</x:v>
-      </x:c>
-      <x:c r="J4" s="80"/>
-      <x:c r="K4" s="80"/>
-      <x:c r="L4" s="80"/>
-      <x:c r="M4" s="80"/>
-      <x:c r="N4" s="80"/>
-      <x:c r="O4" s="80"/>
-      <x:c r="P4" s="80"/>
-      <x:c r="Q4" s="80"/>
-      <x:c r="R4" s="80"/>
-      <x:c r="S4" s="80"/>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="79"/>
-      <x:c r="B5" s="79"/>
-      <x:c r="C5" s="79"/>
-      <x:c r="D5" s="79"/>
-      <x:c r="E5" s="79"/>
-      <x:c r="F5" s="79"/>
+        <x:v>Priority basis</x:v>
+      </x:c>
+      <x:c r="I4" s="108" t="str">
+        <x:v>优先级按任务语义、状态交互、原生 verifier 与当前 Env-Agent co-evolve 研究问题的匹配度判断。</x:v>
+      </x:c>
+      <x:c r="J4" s="108"/>
+      <x:c r="K4" s="108"/>
+      <x:c r="L4" s="108"/>
+      <x:c r="M4" s="108"/>
+      <x:c r="N4"/>
+      <x:c r="O4"/>
+      <x:c r="P4"/>
+      <x:c r="Q4"/>
+      <x:c r="R4"/>
+      <x:c r="S4"/>
+    </x:row>
+    <x:row r="5" ht="28" customHeight="1">
+      <x:c r="A5" s="103" t="str">
+        <x:v>核心实验</x:v>
+      </x:c>
+      <x:c r="B5" s="103" t="str">
+        <x:v>机制验证</x:v>
+      </x:c>
+      <x:c r="C5" s="103" t="str">
+        <x:v>扩展验证</x:v>
+      </x:c>
+      <x:c r="D5" s="103" t="str">
+        <x:v>外部有效性</x:v>
+      </x:c>
+      <x:c r="E5" s="103" t="str">
+        <x:v>参考/对照</x:v>
+      </x:c>
+      <x:c r="F5" s="103" t="str">
+        <x:v>方法与边界</x:v>
+      </x:c>
       <x:c r="G5"/>
       <x:c r="H5" s="79" t="str">
-        <x:v>Decision rule</x:v>
-      </x:c>
-      <x:c r="I5" s="80" t="str">
-        <x:v>P0=总分≥12且运行成本≥1；P1=总分≥8且不同时满足 reset≤1、成本=0；其余 P2。</x:v>
-      </x:c>
-      <x:c r="J5" s="80"/>
-      <x:c r="K5" s="80"/>
-      <x:c r="L5" s="80"/>
-      <x:c r="M5" s="80"/>
-      <x:c r="N5" s="80"/>
-      <x:c r="O5" s="80"/>
-      <x:c r="P5" s="80"/>
-      <x:c r="Q5" s="80"/>
-      <x:c r="R5" s="80"/>
-      <x:c r="S5" s="80"/>
-    </x:row>
-    <x:row r="7" ht="32" customHeight="1">
-      <x:c r="A7" s="74" t="str">
+        <x:v>Reading guide</x:v>
+      </x:c>
+      <x:c r="I5" s="108" t="str">
+        <x:v>每行说明 benchmark 的机制、状态、动作、代表任务、原生评分、适合的六类环境变化，并给出论文与代码/数据直链。</x:v>
+      </x:c>
+      <x:c r="J5" s="108"/>
+      <x:c r="K5" s="108"/>
+      <x:c r="L5" s="108"/>
+      <x:c r="M5" s="108"/>
+      <x:c r="N5"/>
+      <x:c r="O5"/>
+      <x:c r="P5"/>
+      <x:c r="Q5"/>
+      <x:c r="R5"/>
+      <x:c r="S5"/>
+    </x:row>
+    <x:row r="7" ht="38" customHeight="1">
+      <x:c r="A7" s="113" t="str">
         <x:v>Priority</x:v>
       </x:c>
-      <x:c r="B7" s="74" t="str">
-        <x:v>Score</x:v>
-      </x:c>
-      <x:c r="C7" s="74" t="str">
+      <x:c r="B7" s="113" t="str">
         <x:v>Benchmark / testbed</x:v>
       </x:c>
-      <x:c r="D7" s="74" t="str">
-        <x:v>Roadmap role</x:v>
-      </x:c>
-      <x:c r="E7" s="74" t="str">
-        <x:v>Current project anchor</x:v>
-      </x:c>
-      <x:c r="F7" s="74" t="str">
-        <x:v>Domain</x:v>
-      </x:c>
-      <x:c r="G7" s="74" t="str">
-        <x:v>Interface</x:v>
-      </x:c>
-      <x:c r="H7" s="74" t="str">
-        <x:v>First executable slice</x:v>
-      </x:c>
-      <x:c r="I7" s="74" t="str">
-        <x:v>Native verifier</x:v>
-      </x:c>
-      <x:c r="J7" s="74" t="str">
-        <x:v>Reset / snapshot</x:v>
-      </x:c>
-      <x:c r="K7" s="74" t="str">
-        <x:v>Adapter</x:v>
-      </x:c>
-      <x:c r="L7" s="74" t="str">
-        <x:v>Verifier</x:v>
-      </x:c>
-      <x:c r="M7" s="74" t="str">
-        <x:v>Reset</x:v>
-      </x:c>
-      <x:c r="N7" s="74" t="str">
-        <x:v>Six phases</x:v>
-      </x:c>
-      <x:c r="O7" s="74" t="str">
-        <x:v>Diagnostics</x:v>
-      </x:c>
-      <x:c r="P7" s="74" t="str">
-        <x:v>Run cost</x:v>
-      </x:c>
-      <x:c r="Q7" s="74" t="str">
-        <x:v>Transfer</x:v>
-      </x:c>
-      <x:c r="R7" s="74" t="str">
-        <x:v>Next action / reason</x:v>
-      </x:c>
-      <x:c r="S7" s="74" t="str">
+      <x:c r="C7" s="113" t="str">
+        <x:v>Detailed introduction</x:v>
+      </x:c>
+      <x:c r="D7" s="113" t="str">
+        <x:v>Environment and state</x:v>
+      </x:c>
+      <x:c r="E7" s="113" t="str">
+        <x:v>Agent interface / action space</x:v>
+      </x:c>
+      <x:c r="F7" s="113" t="str">
+        <x:v>Representative task example</x:v>
+      </x:c>
+      <x:c r="G7" s="113" t="str">
+        <x:v>Native verifier / success condition</x:v>
+      </x:c>
+      <x:c r="H7" s="113" t="str">
+        <x:v>Suitable environment changes</x:v>
+      </x:c>
+      <x:c r="I7" s="113" t="str">
+        <x:v>Relation to current project</x:v>
+      </x:c>
+      <x:c r="J7" s="113" t="str">
+        <x:v>Paper / project link</x:v>
+      </x:c>
+      <x:c r="K7" s="113" t="str">
+        <x:v>Code / data link</x:v>
+      </x:c>
+      <x:c r="L7" s="113" t="str">
+        <x:v>Research role</x:v>
+      </x:c>
+      <x:c r="M7" s="113" t="str">
         <x:v>Source ID</x:v>
       </x:c>
-    </x:row>
-    <x:row r="8" ht="44" customHeight="1">
-      <x:c r="A8" s="76" t="str">
-        <x:f>IF(AND(B8&gt;=12,P8&gt;=1),"P0",IF(AND(B8&gt;=8,NOT(AND(M8&lt;=1,P8=0))),"P1","P2"))</x:f>
+      <x:c r="N7"/>
+      <x:c r="O7"/>
+      <x:c r="P7"/>
+      <x:c r="Q7"/>
+      <x:c r="R7"/>
+      <x:c r="S7"/>
+    </x:row>
+    <x:row r="8" ht="82" customHeight="1">
+      <x:c r="A8" s="99" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="B8" s="76" t="n">
-        <x:f>SUM(K8:Q8)</x:f>
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C8" s="78" t="str">
+      <x:c r="B8" s="98" t="str">
         <x:v>Local five-scenario suite</x:v>
       </x:c>
-      <x:c r="D8" s="78" t="str">
-        <x:v>Implemented gate</x:v>
-      </x:c>
-      <x:c r="E8" s="78" t="str">
-        <x:v>五个本地场景、六阶段 Harness、Target/Diagnostic</x:v>
-      </x:c>
-      <x:c r="F8" s="78" t="str">
-        <x:v>状态化 API</x:v>
-      </x:c>
-      <x:c r="G8" s="78" t="str">
-        <x:v>JSON tools</x:v>
-      </x:c>
-      <x:c r="H8" s="78" t="str">
-        <x:v>每个场景的 oracle、snapshot、Target replay 与 failure signature</x:v>
-      </x:c>
-      <x:c r="I8" s="78" t="str">
-        <x:v>独立状态 verifier / tests</x:v>
-      </x:c>
-      <x:c r="J8" s="78" t="str">
-        <x:v>完整快照</x:v>
-      </x:c>
-      <x:c r="K8" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="L8" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="M8" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="N8" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="O8" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="P8" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="Q8" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="R8" s="78" t="str">
-        <x:v>冻结一个 Target 配置，建立 baseline→辅助节点→父节点回测矩阵。</x:v>
-      </x:c>
-      <x:c r="S8" s="77" t="str">
+      <x:c r="C8" s="98" t="str">
+        <x:v>本项目自有的五个确定性、可重置、带真实状态 verifier 的最小任务组：exactly-once、订单生命周期、issue workflow、calendar/email 和 code repair。它不是外部排行榜，而是验证环境变化因果效应的第一道门。</x:v>
+      </x:c>
+      <x:c r="D8" s="98" t="str">
+        <x:v>内存数据库、事件日志和微型代码仓库；真实状态、Agent 可见观察、故障注入状态相互分离，并可保存/恢复快照。</x:v>
+      </x:c>
+      <x:c r="E8" s="98" t="str">
+        <x:v>统一 JSON tool call；每个场景只暴露任务所需的读写工具，并经过 adapter 映射到统一 ActionableEnv。</x:v>
+      </x:c>
+      <x:c r="F8" s="98" t="str">
+        <x:v>工具已经提交写入，但响应超时；下一次读取又返回旧值。Agent 必须确认真实状态，避免重复写入，最终只产生一条记录。</x:v>
+      </x:c>
+      <x:c r="G8" s="98" t="str">
+        <x:v>每个场景都有独立 oracle / tests，直接检查真实状态、调用次数、副作用和任务目标；不以模型自评作为成功条件。</x:v>
+      </x:c>
+      <x:c r="H8" s="98" t="str">
+        <x:v>Setup、Contract、f_A、f_T、f_O、Budget 六类全部可测。</x:v>
+      </x:c>
+      <x:c r="I8" s="98" t="str">
+        <x:v>用于先证明：冻结 Target Agent 后，单一环境变化能够稳定修复失败，并且父节点回测不退化；之后才接外部 benchmark。</x:v>
+      </x:c>
+      <x:c r="J8" s="100" t="str">
+        <x:v>https://github.com/mz1622/Env-Agent-rsi</x:v>
+      </x:c>
+      <x:c r="K8" s="100" t="str">
+        <x:v>https://github.com/mz1622/Env-Agent-rsi</x:v>
+      </x:c>
+      <x:c r="L8" s="99" t="str">
+        <x:v>内部回归、机制消融、环境 DAG 单元测试</x:v>
+      </x:c>
+      <x:c r="M8" s="99" t="str">
         <x:v>S00</x:v>
       </x:c>
-    </x:row>
-    <x:row r="9" ht="44" customHeight="1">
-      <x:c r="A9" s="76" t="str">
-        <x:f>IF(AND(B9&gt;=12,P9&gt;=1),"P0",IF(AND(B9&gt;=8,NOT(AND(M9&lt;=1,P9=0))),"P1","P2"))</x:f>
+      <x:c r="N8"/>
+      <x:c r="O8"/>
+      <x:c r="P8"/>
+      <x:c r="Q8"/>
+      <x:c r="R8"/>
+      <x:c r="S8"/>
+    </x:row>
+    <x:row r="9" ht="82" customHeight="1">
+      <x:c r="A9" s="99" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="B9" s="76" t="n">
-        <x:f>SUM(K9:Q9)</x:f>
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C9" s="78" t="str">
+      <x:c r="B9" s="98" t="str">
         <x:v>ToolSandbox</x:v>
       </x:c>
-      <x:c r="D9" s="78" t="str">
-        <x:v>First external pilot</x:v>
-      </x:c>
-      <x:c r="E9" s="78" t="str">
-        <x:v>01 exactly-once；04 calendar/email</x:v>
-      </x:c>
-      <x:c r="F9" s="78" t="str">
-        <x:v>状态化工具 sandbox</x:v>
-      </x:c>
-      <x:c r="G9" s="78" t="str">
-        <x:v>JSON tools</x:v>
-      </x:c>
-      <x:c r="H9" s="78" t="str">
-        <x:v>先选 10 个需要状态依赖和写后确认的任务</x:v>
-      </x:c>
-      <x:c r="I9" s="78" t="str">
-        <x:v>里程碑与 namespace 状态检查</x:v>
-      </x:c>
-      <x:c r="J9" s="78" t="str">
-        <x:v>任务状态可重建</x:v>
-      </x:c>
-      <x:c r="K9" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="L9" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="M9" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="N9" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="O9" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="P9" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="Q9" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="R9" s="78" t="str">
-        <x:v>实现最薄 adapter，验证本地 skill 是否迁移到公开任务。</x:v>
-      </x:c>
-      <x:c r="S9" s="77" t="str">
+      <x:c r="C9" s="98" t="str">
+        <x:v>面向 stateful conversational tool use 的公开 benchmark。任务含隐式状态依赖、工具调用先决条件和分阶段 milestone，特别适合研究工具契约、状态观测与写后确认。</x:v>
+      </x:c>
+      <x:c r="D9" s="98" t="str">
+        <x:v>可执行工具连接到多个 namespace 的可变状态；对话历史、用户请求、工具状态和 milestone 共同定义任务进度。</x:v>
+      </x:c>
+      <x:c r="E9" s="98" t="str">
+        <x:v>函数式 JSON tools；Agent 需要在多轮对话中选择工具、补齐参数，并根据工具返回继续行动。</x:v>
+      </x:c>
+      <x:c r="F9" s="98" t="str">
+        <x:v>用户要求向某联系人发送消息；Agent 先解析联系人和设备/权限状态，再执行发送并确认 milestone，而不是在缺失依赖时盲目重试。</x:v>
+      </x:c>
+      <x:c r="G9" s="98" t="str">
+        <x:v>按 milestone 和最终 namespace 状态检查是否完成关键步骤；可区分表面回复正确与真实副作用正确。</x:v>
+      </x:c>
+      <x:c r="H9" s="98" t="str">
+        <x:v>Setup、Contract、f_A、f_T、f_O、Budget；尤其适合前置依赖、提交后超时和陈旧观察。</x:v>
+      </x:c>
+      <x:c r="I9" s="98" t="str">
+        <x:v>与 exactly-once、calendar/email 两个本地场景最接近，是首个外部迁移试验；可检验本地得到的环境辅助是否跨任务有效。</x:v>
+      </x:c>
+      <x:c r="J9" s="100" t="str">
+        <x:v>https://arxiv.org/abs/2408.04682</x:v>
+      </x:c>
+      <x:c r="K9" s="100" t="str">
+        <x:v>https://github.com/apple/ToolSandbox</x:v>
+      </x:c>
+      <x:c r="L9" s="99" t="str">
+        <x:v>首个外部 stateful tool-use pilot</x:v>
+      </x:c>
+      <x:c r="M9" s="99" t="str">
         <x:v>S34</x:v>
       </x:c>
-    </x:row>
-    <x:row r="10" ht="44" customHeight="1">
-      <x:c r="A10" s="76" t="str">
-        <x:f>IF(AND(B10&gt;=12,P10&gt;=1),"P0",IF(AND(B10&gt;=8,NOT(AND(M10&lt;=1,P10=0))),"P1","P2"))</x:f>
+      <x:c r="N9"/>
+      <x:c r="O9"/>
+      <x:c r="P9"/>
+      <x:c r="Q9"/>
+      <x:c r="R9"/>
+      <x:c r="S9"/>
+    </x:row>
+    <x:row r="10" ht="82" customHeight="1">
+      <x:c r="A10" s="99" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="B10" s="76" t="n">
-        <x:f>SUM(K10:Q10)</x:f>
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C10" s="78" t="str">
+      <x:c r="B10" s="98" t="str">
         <x:v>WorkBench</x:v>
       </x:c>
-      <x:c r="D10" s="78" t="str">
-        <x:v>First external pilot</x:v>
-      </x:c>
-      <x:c r="E10" s="78" t="str">
-        <x:v>04 calendar/email 的直接来源</x:v>
-      </x:c>
-      <x:c r="F10" s="78" t="str">
-        <x:v>办公 API</x:v>
-      </x:c>
-      <x:c r="G10" s="78" t="str">
-        <x:v>26 tools / DB state</x:v>
-      </x:c>
-      <x:c r="H10" s="78" t="str">
-        <x:v>20 个邮件与日历任务，排除纯只读题</x:v>
-      </x:c>
-      <x:c r="I10" s="78" t="str">
-        <x:v>结构化 outcome / 数据库状态</x:v>
-      </x:c>
-      <x:c r="J10" s="78" t="str">
-        <x:v>sandbox 数据可重置</x:v>
-      </x:c>
-      <x:c r="K10" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="L10" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="M10" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="N10" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="O10" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="P10" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="Q10" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="R10" s="78" t="str">
-        <x:v>优先复现本地 calendar/email task 的上游样本，再扩到 20 题。</x:v>
-      </x:c>
-      <x:c r="S10" s="77" t="str">
+      <x:c r="C10" s="98" t="str">
+        <x:v>办公 API benchmark，包含五个 sandbox 数据库、26 个读写工具和 690 个任务。核心不是生成文本，而是让工具调用把工作环境推进到指定 outcome。</x:v>
+      </x:c>
+      <x:c r="D10" s="98" t="str">
+        <x:v>邮件、日历等办公数据库组成可变世界状态；任务可能跨多个对象，并要求正确处理已有事件、冲突和副作用。</x:v>
+      </x:c>
+      <x:c r="E10" s="98" t="str">
+        <x:v>结构化函数调用；工具既可查询也可写入数据库，适合显式区分 read、write、confirm 和 compensate。</x:v>
+      </x:c>
+      <x:c r="F10" s="98" t="str">
+        <x:v>查找逾期任务，为负责人安排最早可用的 30 分钟会议，并发送包含指定信息的邮件；最终结果由数据库状态而非回复措辞决定。</x:v>
+      </x:c>
+      <x:c r="G10" s="98" t="str">
+        <x:v>outcome-centric evaluator 检查最终 sandbox 数据库及副作用，可验证会议、邮件和对象字段是否真正落地。</x:v>
+      </x:c>
+      <x:c r="H10" s="98" t="str">
+        <x:v>Setup、Contract、f_A、f_T、f_O、Budget；可构造身份消歧、时间格式、重复写、陈旧日历读取等变化。</x:v>
+      </x:c>
+      <x:c r="I10" s="98" t="str">
+        <x:v>是本地 calendar/email 场景的直接上游来源；适合先复现相似任务，再扩展到跨数据库 workflow。</x:v>
+      </x:c>
+      <x:c r="J10" s="100" t="str">
+        <x:v>https://arxiv.org/abs/2405.00823</x:v>
+      </x:c>
+      <x:c r="K10" s="100" t="str">
+        <x:v>https://github.com/olly-styles/WorkBench</x:v>
+      </x:c>
+      <x:c r="L10" s="99" t="str">
+        <x:v>办公 API 主 benchmark</x:v>
+      </x:c>
+      <x:c r="M10" s="99" t="str">
         <x:v>S35</x:v>
       </x:c>
-    </x:row>
-    <x:row r="11" ht="44" customHeight="1">
-      <x:c r="A11" s="76" t="str">
-        <x:f>IF(AND(B11&gt;=12,P11&gt;=1),"P0",IF(AND(B11&gt;=8,NOT(AND(M11&lt;=1,P11=0))),"P1","P2"))</x:f>
+      <x:c r="N10"/>
+      <x:c r="O10"/>
+      <x:c r="P10"/>
+      <x:c r="Q10"/>
+      <x:c r="R10"/>
+      <x:c r="S10"/>
+    </x:row>
+    <x:row r="11" ht="82" customHeight="1">
+      <x:c r="A11" s="99" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="B11" s="76" t="n">
-        <x:f>SUM(K11:Q11)</x:f>
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C11" s="78" t="str">
-        <x:v>τ³-bench</x:v>
-      </x:c>
-      <x:c r="D11" s="78" t="str">
-        <x:v>Primary API benchmark</x:v>
-      </x:c>
-      <x:c r="E11" s="78" t="str">
-        <x:v>02 order lifecycle</x:v>
-      </x:c>
-      <x:c r="F11" s="78" t="str">
-        <x:v>零售/航空/电信 API + 用户</x:v>
-      </x:c>
-      <x:c r="G11" s="78" t="str">
-        <x:v>JSON tools + dialogue</x:v>
-      </x:c>
-      <x:c r="H11" s="78" t="str">
-        <x:v>retail base split，scripted user，10 个取消/退款任务</x:v>
-      </x:c>
-      <x:c r="I11" s="78" t="str">
-        <x:v>task criteria + 数据库状态</x:v>
-      </x:c>
-      <x:c r="J11" s="78" t="str">
-        <x:v>domain DB + 对话状态</x:v>
-      </x:c>
-      <x:c r="K11" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="L11" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="M11" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="N11" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="O11" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="P11" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q11" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="R11" s="78" t="str">
-        <x:v>从本地订单动作 codec 迁移；固定 release、user model、seed。</x:v>
-      </x:c>
-      <x:c r="S11" s="77" t="str">
+      <x:c r="B11" s="98" t="str">
+        <x:v>tau3-bench</x:v>
+      </x:c>
+      <x:c r="C11" s="98" t="str">
+        <x:v>面向真实客服代理的多方交互 benchmark：Agent 同时面对用户、业务政策、工具和领域数据库。当前代码仓库持续演进，实验必须固定 release、任务 split、user model 与 seed。</x:v>
+      </x:c>
+      <x:c r="D11" s="98" t="str">
+        <x:v>零售、航空、电信等领域数据库保存订单、账户和工单状态；用户对话状态与后端状态共同决定能否继续。</x:v>
+      </x:c>
+      <x:c r="E11" s="98" t="str">
+        <x:v>JSON tools + 自然语言对话；Agent 既要查询/修改业务对象，也要向用户收集信息、解释政策或请求确认。</x:v>
+      </x:c>
+      <x:c r="F11" s="98" t="str">
+        <x:v>用户要求更换待处理订单中的商品；Agent 验证身份、读取订单、判断政策是否允许，然后执行换货；若条件不满足则走取消或退款流程。</x:v>
+      </x:c>
+      <x:c r="G11" s="98" t="str">
+        <x:v>任务标准与数据库终态联合评分；可用 pass^k 观察同一策略在多次用户模拟中的稳定性。</x:v>
+      </x:c>
+      <x:c r="H11" s="98" t="str">
+        <x:v>Setup、Contract、f_A、f_T、f_O、Budget；特别适合认证、确认 token、政策 guard、事务故障和信息隐藏。</x:v>
+      </x:c>
+      <x:c r="I11" s="98" t="str">
+        <x:v>与本地订单生命周期场景直接对应，也能检验环境辅助是否在真实政策约束和用户交互中仍然有效。</x:v>
+      </x:c>
+      <x:c r="J11" s="100" t="str">
+        <x:v>https://github.com/sierra-research/tau2-bench</x:v>
+      </x:c>
+      <x:c r="K11" s="100" t="str">
+        <x:v>https://github.com/sierra-research/tau2-bench</x:v>
+      </x:c>
+      <x:c r="L11" s="99" t="str">
+        <x:v>客服 API 与多方交互主 benchmark</x:v>
+      </x:c>
+      <x:c r="M11" s="99" t="str">
         <x:v>S37</x:v>
       </x:c>
-    </x:row>
-    <x:row r="12" ht="44" customHeight="1">
-      <x:c r="A12" s="76" t="str">
-        <x:f>IF(AND(B12&gt;=12,P12&gt;=1),"P0",IF(AND(B12&gt;=8,NOT(AND(M12&lt;=1,P12=0))),"P1","P2"))</x:f>
+      <x:c r="N11"/>
+      <x:c r="O11"/>
+      <x:c r="P11"/>
+      <x:c r="Q11"/>
+      <x:c r="R11"/>
+      <x:c r="S11"/>
+    </x:row>
+    <x:row r="12" ht="82" customHeight="1">
+      <x:c r="A12" s="99" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="B12" s="76" t="n">
-        <x:f>SUM(K12:Q12)</x:f>
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C12" s="78" t="str">
+      <x:c r="B12" s="98" t="str">
         <x:v>AppWorld</x:v>
       </x:c>
-      <x:c r="D12" s="78" t="str">
-        <x:v>Primary cross-app benchmark</x:v>
-      </x:c>
-      <x:c r="E12" s="78" t="str">
-        <x:v>03 issue；04 calendar/email</x:v>
-      </x:c>
-      <x:c r="F12" s="78" t="str">
-        <x:v>多应用 API</x:v>
-      </x:c>
-      <x:c r="G12" s="78" t="str">
-        <x:v>Python / JSON APIs</x:v>
-      </x:c>
-      <x:c r="H12" s="78" t="str">
-        <x:v>train/dev 中 20 个有写副作用的 function-calling 任务</x:v>
-      </x:c>
-      <x:c r="I12" s="78" t="str">
-        <x:v>数据库状态单测 + collateral damage</x:v>
-      </x:c>
-      <x:c r="J12" s="78" t="str">
-        <x:v>任务世界与数据库可重置</x:v>
-      </x:c>
-      <x:c r="K12" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="L12" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="M12" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="N12" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="O12" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="P12" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q12" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="R12" s="78" t="str">
-        <x:v>先做 function-calling 子集；保留 test split 作为最终迁移评估。</x:v>
-      </x:c>
-      <x:c r="S12" s="77" t="str">
+      <x:c r="C12" s="98" t="str">
+        <x:v>可控的多应用世界。Agent 使用大量 API 完成跨应用任务；公开任务强调真实数据库变化、复杂依赖和 collateral damage，而不只是单次 function calling。</x:v>
+      </x:c>
+      <x:c r="D12" s="98" t="str">
+        <x:v>多个模拟应用及其数据库构成世界；任务开始时注入用户数据，执行后可直接查询数据库和应用状态。</x:v>
+      </x:c>
+      <x:c r="E12" s="98" t="str">
+        <x:v>Python / JSON 风格 API；动作可跨邮件、日历、待办、购物等应用组合，天然形成长程调用链。</x:v>
+      </x:c>
+      <x:c r="F12" s="98" t="str">
+        <x:v>从邮件中找出会议请求，在日历中创建事件，并把后续事项写入待办；所有对象必须关联到正确联系人和时间。</x:v>
+      </x:c>
+      <x:c r="G12" s="98" t="str">
+        <x:v>通过数据库状态单元测试验证目标，并检查不应发生的 collateral damage；适合严格保持 verifier 不变。</x:v>
+      </x:c>
+      <x:c r="H12" s="98" t="str">
+        <x:v>Setup、Contract、f_A、f_T、f_O、Budget 六类均可覆盖；尤其适合跨应用 observation 与 action contract。</x:v>
+      </x:c>
+      <x:c r="I12" s="98" t="str">
+        <x:v>把本地 issue、calendar/email 扩展为跨应用组合任务，是验证环境 DAG 是否能处理长程依赖的核心外部环境。</x:v>
+      </x:c>
+      <x:c r="J12" s="100" t="str">
+        <x:v>https://arxiv.org/abs/2407.18901</x:v>
+      </x:c>
+      <x:c r="K12" s="100" t="str">
+        <x:v>https://github.com/StonyBrookNLP/appworld</x:v>
+      </x:c>
+      <x:c r="L12" s="99" t="str">
+        <x:v>跨应用主 benchmark</x:v>
+      </x:c>
+      <x:c r="M12" s="99" t="str">
         <x:v>S03</x:v>
       </x:c>
-    </x:row>
-    <x:row r="13" ht="44" customHeight="1">
-      <x:c r="A13" s="76" t="str">
-        <x:f>IF(AND(B13&gt;=12,P13&gt;=1),"P0",IF(AND(B13&gt;=8,NOT(AND(M13&lt;=1,P13=0))),"P1","P2"))</x:f>
+      <x:c r="N12"/>
+      <x:c r="O12"/>
+      <x:c r="P12"/>
+      <x:c r="Q12"/>
+      <x:c r="R12"/>
+      <x:c r="S12"/>
+    </x:row>
+    <x:row r="13" ht="82" customHeight="1">
+      <x:c r="A13" s="99" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="B13" s="76" t="n">
-        <x:f>SUM(K13:Q13)</x:f>
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C13" s="78" t="str">
+      <x:c r="B13" s="98" t="str">
         <x:v>EnvHarness toy24</x:v>
       </x:c>
-      <x:c r="D13" s="78" t="str">
-        <x:v>Protocol compatibility smoke</x:v>
-      </x:c>
-      <x:c r="E13" s="78" t="str">
-        <x:v>BenchmarkAdapter 与六阶段 Harness</x:v>
-      </x:c>
-      <x:c r="F13" s="78" t="str">
-        <x:v>内存 toy env</x:v>
-      </x:c>
-      <x:c r="G13" s="78" t="str">
-        <x:v>reset / step</x:v>
-      </x:c>
-      <x:c r="H13" s="78" t="str">
-        <x:v>运行官方 check 与 snapshot round-trip</x:v>
-      </x:c>
-      <x:c r="I13" s="78" t="str">
-        <x:v>确定性目标谓词</x:v>
-      </x:c>
-      <x:c r="J13" s="78" t="str">
-        <x:v>完整 save/load</x:v>
-      </x:c>
-      <x:c r="K13" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="L13" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="M13" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="N13" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="O13" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P13" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="Q13" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R13" s="78" t="str">
-        <x:v>只用于验证 Bridge/规则语义，不作为环境辅助效果主结论。</x:v>
-      </x:c>
-      <x:c r="S13" s="77" t="str">
+      <x:c r="C13" s="98" t="str">
+        <x:v>EnvHarness 提供的轻量环境兼容性样例：给定四个数字，用合法算术运算得到 24。任务本身很小，但适合验证 adapter、snapshot 和环境变换协议是否一致。</x:v>
+      </x:c>
+      <x:c r="D13" s="98" t="str">
+        <x:v>状态由剩余数字、已执行表达式、合法动作和终止标志构成；可完全重建并快速重复运行。</x:v>
+      </x:c>
+      <x:c r="E13" s="98" t="str">
+        <x:v>reset / step 或等价的离散动作接口；动作边界明确，便于检查 wrapper 是否改变了语义。</x:v>
+      </x:c>
+      <x:c r="F13" s="98" t="str">
+        <x:v>给定 4、7、8、8，逐步选择数字与运算符形成合法表达式，最终结果必须等于 24 且每个输入只使用一次。</x:v>
+      </x:c>
+      <x:c r="G13" s="98" t="str">
+        <x:v>确定性目标谓词检查表达式合法性、输入使用次数和最终数值；snapshot round-trip 后结果必须相同。</x:v>
+      </x:c>
+      <x:c r="H13" s="98" t="str">
+        <x:v>Setup、Contract、f_A、f_T、f_O、Budget；主要用于协议 smoke test，而非复杂业务结论。</x:v>
+      </x:c>
+      <x:c r="I13" s="98" t="str">
+        <x:v>可快速发现 adapter 或六阶段 harness 的实现错误，防止把基础设施 bug 误判为 Agent 能力问题。</x:v>
+      </x:c>
+      <x:c r="J13" s="100" t="str">
+        <x:v>https://arxiv.org/abs/2608.19880</x:v>
+      </x:c>
+      <x:c r="K13" s="100" t="str">
+        <x:v>https://github.com/google-research/envharness</x:v>
+      </x:c>
+      <x:c r="L13" s="99" t="str">
+        <x:v>协议兼容与 smoke test</x:v>
+      </x:c>
+      <x:c r="M13" s="99" t="str">
         <x:v>S02</x:v>
       </x:c>
-    </x:row>
-    <x:row r="14" ht="44" customHeight="1">
-      <x:c r="A14" s="76" t="str">
-        <x:f>IF(AND(B14&gt;=12,P14&gt;=1),"P0",IF(AND(B14&gt;=8,NOT(AND(M14&lt;=1,P14=0))),"P1","P2"))</x:f>
+      <x:c r="N13"/>
+      <x:c r="O13"/>
+      <x:c r="P13"/>
+      <x:c r="Q13"/>
+      <x:c r="R13"/>
+      <x:c r="S13"/>
+    </x:row>
+    <x:row r="14" ht="82" customHeight="1">
+      <x:c r="A14" s="99" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B14" s="76" t="n">
-        <x:f>SUM(K14:Q14)</x:f>
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C14" s="78" t="str">
+      <x:c r="B14" s="98" t="str">
         <x:v>SWE-bench Verified</x:v>
       </x:c>
-      <x:c r="D14" s="78" t="str">
-        <x:v>Code benchmark pilot</x:v>
-      </x:c>
-      <x:c r="E14" s="78" t="str">
-        <x:v>05 code repair</x:v>
-      </x:c>
-      <x:c r="F14" s="78" t="str">
-        <x:v>容器化代码仓库</x:v>
-      </x:c>
-      <x:c r="G14" s="78" t="str">
-        <x:v>shell + file tools</x:v>
-      </x:c>
-      <x:c r="H14" s="78" t="str">
-        <x:v>10 个 Python、构建快、测试稳定的 Verified task</x:v>
-      </x:c>
-      <x:c r="I14" s="78" t="str">
-        <x:v>FAIL_TO_PASS + PASS_TO_PASS</x:v>
-      </x:c>
-      <x:c r="J14" s="78" t="str">
-        <x:v>镜像 + git diff 重建</x:v>
-      </x:c>
-      <x:c r="K14" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="L14" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="M14" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="N14" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="O14" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="P14" s="76" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q14" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="R14" s="78" t="str">
-        <x:v>先复用本地代码工具 schema；内环只跑小子集并缓存基础镜像。</x:v>
-      </x:c>
-      <x:c r="S14" s="77" t="str">
+      <x:c r="C14" s="98" t="str">
+        <x:v>真实 GitHub issue 级代码修复 benchmark。Agent 获得仓库和问题描述，在隔离环境中定位缺陷、编辑代码并让测试通过；Verified 子集降低了原始任务歧义。</x:v>
+      </x:c>
+      <x:c r="D14" s="98" t="str">
+        <x:v>容器化仓库、依赖、测试状态和 git diff 构成环境；文件改动和命令输出是主要可观察状态。</x:v>
+      </x:c>
+      <x:c r="E14" s="98" t="str">
+        <x:v>shell、文件读取/编辑、测试命令；动作空间开放，但可以由 adapter 统一成 terminal/file tools。</x:v>
+      </x:c>
+      <x:c r="F14" s="98" t="str">
+        <x:v>Astropy 的 QDP 解析器不能处理小写命令：Agent 定位 parser、补丁实现并增加/运行测试，同时保证已有行为不退化。</x:v>
+      </x:c>
+      <x:c r="G14" s="98" t="str">
+        <x:v>FAIL_TO_PASS 测试必须转为通过，PASS_TO_PASS 测试仍保持通过；最终以真实执行结果评分。</x:v>
+      </x:c>
+      <x:c r="H14" s="98" t="str">
+        <x:v>Setup、Contract、f_A、f_T、f_O、Budget；可改变 repo 定位、工具 schema、命令失败、日志截断和测试预算。</x:v>
+      </x:c>
+      <x:c r="I14" s="98" t="str">
+        <x:v>对应本地 code repair 场景；适合验证环境辅助是否能在开放动作空间里缩小问题边界，而不是修改 Agent 本身。</x:v>
+      </x:c>
+      <x:c r="J14" s="100" t="str">
+        <x:v>https://arxiv.org/abs/2310.06770</x:v>
+      </x:c>
+      <x:c r="K14" s="100" t="str">
+        <x:v>https://github.com/SWE-bench/SWE-bench | https://huggingface.co/datasets/SWE-bench/SWE-bench_Verified</x:v>
+      </x:c>
+      <x:c r="L14" s="99" t="str">
+        <x:v>真实代码修复外部验证</x:v>
+      </x:c>
+      <x:c r="M14" s="99" t="str">
         <x:v>S09</x:v>
       </x:c>
-    </x:row>
-    <x:row r="15" ht="44" customHeight="1">
-      <x:c r="A15" s="76" t="str">
-        <x:f>IF(AND(B15&gt;=12,P15&gt;=1),"P0",IF(AND(B15&gt;=8,NOT(AND(M15&lt;=1,P15=0))),"P1","P2"))</x:f>
+      <x:c r="N14"/>
+      <x:c r="O14"/>
+      <x:c r="P14"/>
+      <x:c r="Q14"/>
+      <x:c r="R14"/>
+      <x:c r="S14"/>
+    </x:row>
+    <x:row r="15" ht="82" customHeight="1">
+      <x:c r="A15" s="99" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B15" s="76" t="n">
-        <x:f>SUM(K15:Q15)</x:f>
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C15" s="78" t="str">
+      <x:c r="B15" s="98" t="str">
         <x:v>ALFWorld</x:v>
       </x:c>
-      <x:c r="D15" s="78" t="str">
-        <x:v>Cross-domain control</x:v>
-      </x:c>
-      <x:c r="E15" s="78" t="str">
-        <x:v>验证 Setup/Observation 跨域性</x:v>
-      </x:c>
-      <x:c r="F15" s="78" t="str">
-        <x:v>文本具身</x:v>
-      </x:c>
-      <x:c r="G15" s="78" t="str">
-        <x:v>text action</x:v>
-      </x:c>
-      <x:c r="H15" s="78" t="str">
-        <x:v>TextWorld 模式单一 act(command) adapter</x:v>
-      </x:c>
-      <x:c r="I15" s="78" t="str">
-        <x:v>环境目标谓词</x:v>
-      </x:c>
-      <x:c r="J15" s="78" t="str">
-        <x:v>固定 task/seed</x:v>
-      </x:c>
-      <x:c r="K15" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="L15" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="M15" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="N15" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="O15" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P15" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="Q15" s="76" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R15" s="78" t="str">
-        <x:v>作为跨域对照，避免把 API 副作用结论误当作普遍规律。</x:v>
-      </x:c>
-      <x:c r="S15" s="77" t="str">
+      <x:c r="C15" s="98" t="str">
+        <x:v>把具身家务任务抽象为文本交互的 benchmark，结合高层语言目标与可执行环境状态。它可作为跨域对照，测试我们的变化类型是否只对 API 工具有效。</x:v>
+      </x:c>
+      <x:c r="D15" s="98" t="str">
+        <x:v>房间、容器、物体位置以及 clean/heat/cool 等属性组成可变世界状态；任务和随机种子可重建。</x:v>
+      </x:c>
+      <x:c r="E15" s="98" t="str">
+        <x:v>单一 text action，如 go、open、take、clean、heat、put；action codec 简单但状态前置条件明确。</x:v>
+      </x:c>
+      <x:c r="F15" s="98" t="str">
+        <x:v>找到杯子，先清洗或加热，再放入指定容器；Agent 必须探索位置并按正确顺序满足状态谓词。</x:v>
+      </x:c>
+      <x:c r="G15" s="98" t="str">
+        <x:v>环境目标谓词直接检查物体位置和属性；非法动作与未满足前置条件可被明确识别。</x:v>
+      </x:c>
+      <x:c r="H15" s="98" t="str">
+        <x:v>Setup、Contract、f_A、f_T、f_O、Budget；尤其适合观察遮蔽、动作 guard 和 step budget。</x:v>
+      </x:c>
+      <x:c r="I15" s="98" t="str">
+        <x:v>作为非办公、非代码域对照，帮助判断六类环境变化是否具有跨域普适性。</x:v>
+      </x:c>
+      <x:c r="J15" s="100" t="str">
+        <x:v>https://arxiv.org/abs/2010.03768</x:v>
+      </x:c>
+      <x:c r="K15" s="100" t="str">
+        <x:v>https://github.com/alfworld/alfworld</x:v>
+      </x:c>
+      <x:c r="L15" s="99" t="str">
+        <x:v>跨域状态控制对照</x:v>
+      </x:c>
+      <x:c r="M15" s="99" t="str">
         <x:v>S05</x:v>
       </x:c>
-    </x:row>
-    <x:row r="16" ht="44" customHeight="1">
-      <x:c r="A16" s="76" t="str">
-        <x:f>IF(AND(B16&gt;=12,P16&gt;=1),"P0",IF(AND(B16&gt;=8,NOT(AND(M16&lt;=1,P16=0))),"P1","P2"))</x:f>
+      <x:c r="N15"/>
+      <x:c r="O15"/>
+      <x:c r="P15"/>
+      <x:c r="Q15"/>
+      <x:c r="R15"/>
+      <x:c r="S15"/>
+    </x:row>
+    <x:row r="16" ht="82" customHeight="1">
+      <x:c r="A16" s="99" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B16" s="76" t="n">
-        <x:f>SUM(K16:Q16)</x:f>
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C16" s="78" t="str">
+      <x:c r="B16" s="98" t="str">
         <x:v>Terminal-Bench 2.0</x:v>
       </x:c>
-      <x:c r="D16" s="78" t="str">
-        <x:v>Terminal generalization</x:v>
-      </x:c>
-      <x:c r="E16" s="78" t="str">
-        <x:v>05 code repair 的扩展</x:v>
-      </x:c>
-      <x:c r="F16" s="78" t="str">
-        <x:v>容器化终端</x:v>
-      </x:c>
-      <x:c r="G16" s="78" t="str">
-        <x:v>shell actions</x:v>
-      </x:c>
-      <x:c r="H16" s="78" t="str">
-        <x:v>先选 10 个无网络、短构建任务</x:v>
-      </x:c>
-      <x:c r="I16" s="78" t="str">
-        <x:v>容器内综合测试</x:v>
-      </x:c>
-      <x:c r="J16" s="78" t="str">
-        <x:v>每任务独立环境</x:v>
-      </x:c>
-      <x:c r="K16" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="L16" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="M16" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="N16" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="O16" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="P16" s="76" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q16" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R16" s="78" t="str">
-        <x:v>复用 shell codec 与 Budget；任务异构，不能直接自动生成 mutation。</x:v>
-      </x:c>
-      <x:c r="S16" s="77" t="str">
+      <x:c r="C16" s="98" t="str">
+        <x:v>在真实终端容器中完成复杂、端到端工程任务的 benchmark，覆盖编译、服务配置、数据处理和系统操作。任务比单文件代码修复更接近开放工作环境。</x:v>
+      </x:c>
+      <x:c r="D16" s="98" t="str">
+        <x:v>每个任务运行在独立容器中；文件系统、进程、服务和命令历史共同形成状态，通常可从镜像重建。</x:v>
+      </x:c>
+      <x:c r="E16" s="98" t="str">
+        <x:v>shell commands 与文件操作；动作空间开放，Agent 需要自行选择工具链、检查输出并决定终止。</x:v>
+      </x:c>
+      <x:c r="F16" s="98" t="str">
+        <x:v>配置一个服务或修复构建流程，使指定进程、文件和测试同时达到目标状态；只修改表面输出不能通过 evaluator。</x:v>
+      </x:c>
+      <x:c r="G16" s="98" t="str">
+        <x:v>容器内综合测试和任务专用 verifier 检查最终状态；Terminal-Bench 2.0 论文描述了 89 个真实工作流任务。</x:v>
+      </x:c>
+      <x:c r="H16" s="98" t="str">
+        <x:v>Setup、Contract、f_A、f_T、f_O、Budget；特别适合命令安全 guard、非零退出、日志截断与资源预算。</x:v>
+      </x:c>
+      <x:c r="I16" s="98" t="str">
+        <x:v>扩展本地 code repair 到系统级工作流；用于检验环境辅助在开放 action space 中能否稳定减少无效搜索。</x:v>
+      </x:c>
+      <x:c r="J16" s="100" t="str">
+        <x:v>https://arxiv.org/abs/2601.11868</x:v>
+      </x:c>
+      <x:c r="K16" s="100" t="str">
+        <x:v>https://github.com/jvpoulos/terminal-bench</x:v>
+      </x:c>
+      <x:c r="L16" s="99" t="str">
+        <x:v>终端任务泛化</x:v>
+      </x:c>
+      <x:c r="M16" s="99" t="str">
         <x:v>S16</x:v>
       </x:c>
-    </x:row>
-    <x:row r="17" ht="44" customHeight="1">
-      <x:c r="A17" s="76" t="str">
-        <x:f>IF(AND(B17&gt;=12,P17&gt;=1),"P0",IF(AND(B17&gt;=8,NOT(AND(M17&lt;=1,P17=0))),"P1","P2"))</x:f>
+      <x:c r="N16"/>
+      <x:c r="O16"/>
+      <x:c r="P16"/>
+      <x:c r="Q16"/>
+      <x:c r="R16"/>
+      <x:c r="S16"/>
+    </x:row>
+    <x:row r="17" ht="82" customHeight="1">
+      <x:c r="A17" s="99" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B17" s="76" t="n">
-        <x:f>SUM(K17:Q17)</x:f>
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C17" s="78" t="str">
+      <x:c r="B17" s="98" t="str">
         <x:v>WebShop</x:v>
       </x:c>
-      <x:c r="D17" s="78" t="str">
-        <x:v>Simulated web control</x:v>
-      </x:c>
-      <x:c r="E17" s="78" t="str">
-        <x:v>03 workflow 的浏览器前置验证</x:v>
-      </x:c>
-      <x:c r="F17" s="78" t="str">
-        <x:v>模拟电商网页</x:v>
-      </x:c>
-      <x:c r="G17" s="78" t="str">
-        <x:v>browser actions</x:v>
-      </x:c>
-      <x:c r="H17" s="78" t="str">
-        <x:v>small 商品集上的搜索→选择→购买任务</x:v>
-      </x:c>
-      <x:c r="I17" s="78" t="str">
-        <x:v>属性匹配奖励</x:v>
-      </x:c>
-      <x:c r="J17" s="78" t="str">
-        <x:v>站点可重置</x:v>
-      </x:c>
-      <x:c r="K17" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="L17" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M17" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="N17" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="O17" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P17" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q17" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R17" s="78" t="str">
-        <x:v>先验证 Browser adapter 的动作/观察变化，再进入多站点环境。</x:v>
-      </x:c>
-      <x:c r="S17" s="77" t="str">
+      <x:c r="C17" s="98" t="str">
+        <x:v>模拟电商网站上的目标导向浏览 benchmark。任务给出自然语言购买约束，Agent 需要搜索、筛选、查看商品并选择满足属性的选项。</x:v>
+      </x:c>
+      <x:c r="D17" s="98" t="str">
+        <x:v>站点目录、搜索结果、商品属性、当前页面、购物车和购买状态构成可重置环境。</x:v>
+      </x:c>
+      <x:c r="E17" s="98" t="str">
+        <x:v>浏览器式 click/search/back/choose actions；比真实网页更稳定，适合先验证 browser adapter。</x:v>
+      </x:c>
+      <x:c r="F17" s="98" t="str">
+        <x:v>购买价格低于预算、指定颜色与容量的商品；Agent 要区分标题相似但属性不符的候选并选中正确 variant。</x:v>
+      </x:c>
+      <x:c r="G17" s="98" t="str">
+        <x:v>基于目标属性匹配和购买终态给出奖励；能区分部分匹配与完全成功。</x:v>
+      </x:c>
+      <x:c r="H17" s="98" t="str">
+        <x:v>Setup、Contract、f_A、f_T、f_O、Budget；适合搜索结果截断、页面观察、错误点击保护与步数预算。</x:v>
+      </x:c>
+      <x:c r="I17" s="98" t="str">
+        <x:v>在进入多站点 WebArena 前提供稳定 browser 控制面，先验证观察和动作变化不会破坏任务语义。</x:v>
+      </x:c>
+      <x:c r="J17" s="100" t="str">
+        <x:v>https://arxiv.org/abs/2207.01206</x:v>
+      </x:c>
+      <x:c r="K17" s="100" t="str">
+        <x:v>https://github.com/princeton-nlp/WebShop</x:v>
+      </x:c>
+      <x:c r="L17" s="99" t="str">
+        <x:v>模拟网页控制 pilot</x:v>
+      </x:c>
+      <x:c r="M17" s="99" t="str">
         <x:v>S06</x:v>
       </x:c>
-    </x:row>
-    <x:row r="18" ht="44" customHeight="1">
-      <x:c r="A18" s="76" t="str">
-        <x:f>IF(AND(B18&gt;=12,P18&gt;=1),"P0",IF(AND(B18&gt;=8,NOT(AND(M18&lt;=1,P18=0))),"P1","P2"))</x:f>
+      <x:c r="N17"/>
+      <x:c r="O17"/>
+      <x:c r="P17"/>
+      <x:c r="Q17"/>
+      <x:c r="R17"/>
+      <x:c r="S17"/>
+    </x:row>
+    <x:row r="18" ht="82" customHeight="1">
+      <x:c r="A18" s="99" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B18" s="76" t="n">
-        <x:f>SUM(K18:Q18)</x:f>
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C18" s="78" t="str">
+      <x:c r="B18" s="98" t="str">
         <x:v>SpreadsheetBench 2</x:v>
       </x:c>
-      <x:c r="D18" s="78" t="str">
-        <x:v>File side-effect benchmark</x:v>
-      </x:c>
-      <x:c r="E18" s="78" t="str">
-        <x:v>BenchmarkAdapter + 文件快照</x:v>
-      </x:c>
-      <x:c r="F18" s="78" t="str">
-        <x:v>电子表格</x:v>
-      </x:c>
-      <x:c r="G18" s="78" t="str">
-        <x:v>file / spreadsheet tools</x:v>
-      </x:c>
-      <x:c r="H18" s="78" t="str">
-        <x:v>只选确定性单表编辑任务，排除 VLM evaluator 类</x:v>
-      </x:c>
-      <x:c r="I18" s="78" t="str">
-        <x:v>工作簿结果 evaluator</x:v>
-      </x:c>
-      <x:c r="J18" s="78" t="str">
-        <x:v>输入文件副本</x:v>
-      </x:c>
-      <x:c r="K18" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="L18" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="M18" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="N18" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="O18" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P18" s="76" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q18" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R18" s="78" t="str">
-        <x:v>适合文件写后确认；先统一 workbook hash 与重算协议。</x:v>
-      </x:c>
-      <x:c r="S18" s="77" t="str">
+      <x:c r="C18" s="98" t="str">
+        <x:v>评估 Agent 对真实电子表格进行分析和编辑的 benchmark，既包含公式与数据逻辑，也包含格式和文件副作用；结果必须落到工作簿而不是只给文字答案。</x:v>
+      </x:c>
+      <x:c r="D18" s="98" t="str">
+        <x:v>输入工作簿、单元格公式、样式、命名区域和重算结果组成状态；每次任务可从原始文件副本重置。</x:v>
+      </x:c>
+      <x:c r="E18" s="98" t="str">
+        <x:v>文件/电子表格工具，包括读写 range、公式、格式和保存；可通过 adapter 记录细粒度变更。</x:v>
+      </x:c>
+      <x:c r="F18" s="98" t="str">
+        <x:v>修复汇总表中引用错误的公式，保持其他公式与格式不变，并保存成指定文件；重算后总计必须正确。</x:v>
+      </x:c>
+      <x:c r="G18" s="98" t="str">
+        <x:v>工作簿结果 evaluator 检查目标单元格、公式、格式和保存产物；可结合 hash 排除非目标改动。</x:v>
+      </x:c>
+      <x:c r="H18" s="98" t="str">
+        <x:v>Setup、Contract、f_A、f_T、f_O、Budget；适合文件版本、写入确认、局部观察和操作预算。</x:v>
+      </x:c>
+      <x:c r="I18" s="98" t="str">
+        <x:v>提供与数据库不同的文件型副作用，可验证 snapshot/verifier 边界能否推广到复杂文档状态。</x:v>
+      </x:c>
+      <x:c r="J18" s="100" t="str">
+        <x:v>https://github.com/RUCKBReasoning/SpreadsheetBench-2</x:v>
+      </x:c>
+      <x:c r="K18" s="100" t="str">
+        <x:v>https://github.com/RUCKBReasoning/SpreadsheetBench-2 | https://huggingface.co/datasets/KAKA22/SpreadsheetBench-v2</x:v>
+      </x:c>
+      <x:c r="L18" s="99" t="str">
+        <x:v>文件副作用 benchmark</x:v>
+      </x:c>
+      <x:c r="M18" s="99" t="str">
         <x:v>S11</x:v>
       </x:c>
-    </x:row>
-    <x:row r="19" ht="44" customHeight="1">
-      <x:c r="A19" s="76" t="str">
-        <x:f>IF(AND(B19&gt;=12,P19&gt;=1),"P0",IF(AND(B19&gt;=8,NOT(AND(M19&lt;=1,P19=0))),"P1","P2"))</x:f>
+      <x:c r="N18"/>
+      <x:c r="O18"/>
+      <x:c r="P18"/>
+      <x:c r="Q18"/>
+      <x:c r="R18"/>
+      <x:c r="S18"/>
+    </x:row>
+    <x:row r="19" ht="82" customHeight="1">
+      <x:c r="A19" s="99" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="B19" s="98" t="str">
+        <x:v>WebArena-Verified</x:v>
+      </x:c>
+      <x:c r="C19" s="98" t="str">
+        <x:v>对 WebArena 任务和 evaluator 进行审计、修复后的网页 Agent benchmark。覆盖 GitLab、论坛、购物等自托管站点，更强调可重复和可靠评分。</x:v>
+      </x:c>
+      <x:c r="D19" s="98" t="str">
+        <x:v>多个网站的数据库、页面和会话状态构成环境；任务通常跨页面且带真实写副作用，可通过站点镜像重建。</x:v>
+      </x:c>
+      <x:c r="E19" s="98" t="str">
+        <x:v>BrowserGym / Playwright 风格浏览器动作，包含点击、输入、导航和页面观察。</x:v>
+      </x:c>
+      <x:c r="F19" s="98" t="str">
+        <x:v>在 GitLab 中找到指定 issue，分配给正确成员、添加评论并更新状态；每个副作用都必须作用于正确对象。</x:v>
+      </x:c>
+      <x:c r="G19" s="98" t="str">
+        <x:v>结合页面响应、后端状态或 network trace 的 task evaluator 检查结果，降低仅靠 DOM 文本判断的误差。</x:v>
+      </x:c>
+      <x:c r="H19" s="98" t="str">
+        <x:v>Setup、Contract、f_A、f_T、f_O、Budget；适合登录定位、元素约束、网络失败、观察压缩和步数预算。</x:v>
+      </x:c>
+      <x:c r="I19" s="98" t="str">
+        <x:v>对应本地 issue workflow，是 browser 环境中验证同一失败签名与环境修复能否迁移的关键场景。</x:v>
+      </x:c>
+      <x:c r="J19" s="100" t="str">
+        <x:v>https://github.com/ServiceNow/webarena-verified</x:v>
+      </x:c>
+      <x:c r="K19" s="100" t="str">
+        <x:v>https://github.com/ServiceNow/webarena-verified | https://huggingface.co/datasets/AmineHA/WebArena-Verified</x:v>
+      </x:c>
+      <x:c r="L19" s="99" t="str">
+        <x:v>经审计的真实网页主 benchmark</x:v>
+      </x:c>
+      <x:c r="M19" s="99" t="str">
+        <x:v>S36</x:v>
+      </x:c>
+      <x:c r="N19"/>
+      <x:c r="O19"/>
+      <x:c r="P19"/>
+      <x:c r="Q19"/>
+      <x:c r="R19"/>
+      <x:c r="S19"/>
+    </x:row>
+    <x:row r="20" ht="82" customHeight="1">
+      <x:c r="A20" s="99" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="B20" s="98" t="str">
+        <x:v>WorkArena / WorkArena++</x:v>
+      </x:c>
+      <x:c r="C20" s="98" t="str">
+        <x:v>基于 ServiceNow 的企业知识工作 benchmark。WorkArena 包含原子任务，WorkArena++ 将它们组合成长程 workflow，覆盖表单、列表、知识库、服务目录和仪表盘。</x:v>
+      </x:c>
+      <x:c r="D20" s="98" t="str">
+        <x:v>ServiceNow 实例中的记录、表单、目录订单、知识库和用户会话形成持久状态；实例需要可靠 reset。</x:v>
+      </x:c>
+      <x:c r="E20" s="98" t="str">
+        <x:v>BrowserGym 浏览器动作；Agent 通过 UI 完成工作而不是直接访问数据库。</x:v>
+      </x:c>
+      <x:c r="F20" s="98" t="str">
+        <x:v>在知识库查询政策后，筛选相关工单、更新字段并通过服务目录提交正确配置的请求。</x:v>
+      </x:c>
+      <x:c r="G20" s="98" t="str">
+        <x:v>程序化 task evaluator 检查 ServiceNow 后端记录与页面结果；组合任务可评估中间进度和最终完成。</x:v>
+      </x:c>
+      <x:c r="H20" s="98" t="str">
+        <x:v>Setup、Contract、f_A、f_T、f_O、Budget；适合认证、表单 schema、UI guard、页面延迟和长程预算。</x:v>
+      </x:c>
+      <x:c r="I20" s="98" t="str">
+        <x:v>用于把 issue/calendar 类任务迁移到企业 GUI；能测试环境辅助是否在 API 不可见时仍然有效。</x:v>
+      </x:c>
+      <x:c r="J20" s="100" t="str">
+        <x:v>https://github.com/ServiceNow/WorkArena</x:v>
+      </x:c>
+      <x:c r="K20" s="100" t="str">
+        <x:v>https://github.com/ServiceNow/WorkArena | https://github.com/ServiceNow/BrowserGym</x:v>
+      </x:c>
+      <x:c r="L20" s="99" t="str">
+        <x:v>企业网页长程验证</x:v>
+      </x:c>
+      <x:c r="M20" s="99" t="str">
+        <x:v>S08</x:v>
+      </x:c>
+      <x:c r="N20"/>
+      <x:c r="O20"/>
+      <x:c r="P20"/>
+      <x:c r="Q20"/>
+      <x:c r="R20"/>
+      <x:c r="S20"/>
+    </x:row>
+    <x:row r="21" ht="82" customHeight="1">
+      <x:c r="A21" s="99" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="B21" s="98" t="str">
+        <x:v>AndroidWorld</x:v>
+      </x:c>
+      <x:c r="C21" s="98" t="str">
+        <x:v>运行在真实 Android emulator 上的动态 benchmark。公开实现包含 116 个手工任务、20 个应用，并通过随机参数生成大量任务变体。</x:v>
+      </x:c>
+      <x:c r="D21" s="98" t="str">
+        <x:v>模拟器、应用数据库、当前屏幕、系统设置和动态任务参数组成状态；setup 和 teardown 由任务代码控制。</x:v>
+      </x:c>
+      <x:c r="E21" s="98" t="str">
+        <x:v>触摸、输入、返回、应用启动等移动端动作，并结合截图或 accessibility 信息观察。</x:v>
+      </x:c>
+      <x:c r="F21" s="98" t="str">
+        <x:v>创建指定联系人或闹钟，随后通过应用状态确认字段和时间正确；参数每次运行可变化。</x:v>
+      </x:c>
+      <x:c r="G21" s="98" t="str">
+        <x:v>任务提供 durable success signal，并通过 setup/success/teardown 控制可重复性。</x:v>
+      </x:c>
+      <x:c r="H21" s="98" t="str">
+        <x:v>Setup、Contract、f_A、f_T、f_O、Budget；适合动态参数、触摸约束、应用延迟、视觉观察和步数预算。</x:v>
+      </x:c>
+      <x:c r="I21" s="98" t="str">
+        <x:v>参数化任务和可靠 reward 值得借鉴，可在后期检验环境 DAG 是否能跨设备实例复用变化。</x:v>
+      </x:c>
+      <x:c r="J21" s="100" t="str">
+        <x:v>https://arxiv.org/abs/2405.14573</x:v>
+      </x:c>
+      <x:c r="K21" s="100" t="str">
+        <x:v>https://github.com/google-research/android_world</x:v>
+      </x:c>
+      <x:c r="L21" s="99" t="str">
+        <x:v>移动端参数化外部验证</x:v>
+      </x:c>
+      <x:c r="M21" s="99" t="str">
+        <x:v>S15</x:v>
+      </x:c>
+      <x:c r="N21"/>
+      <x:c r="O21"/>
+      <x:c r="P21"/>
+      <x:c r="Q21"/>
+      <x:c r="R21"/>
+      <x:c r="S21"/>
+    </x:row>
+    <x:row r="22" ht="82" customHeight="1">
+      <x:c r="A22" s="99" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="B22" s="98" t="str">
+        <x:v>OSWorld 2.1</x:v>
+      </x:c>
+      <x:c r="C22" s="98" t="str">
+        <x:v>面向真实桌面和跨应用长程工作流的 computer-use benchmark。OSWorld 2.1 是当前推荐的修订版本，任务、资产、网站和 provider image 需要按 release 固定。</x:v>
+      </x:c>
+      <x:c r="D22" s="98" t="str">
+        <x:v>虚拟机中的桌面、文件系统、应用、网页和凭据共同构成复杂状态；通过镜像与任务 setup 恢复。</x:v>
+      </x:c>
+      <x:c r="E22" s="98" t="str">
+        <x:v>鼠标、键盘、截图、accessibility/GUI 操作；动作空间开放且跨应用。</x:v>
+      </x:c>
+      <x:c r="F22" s="98" t="str">
+        <x:v>在文档与电子表格间提取信息、修改文件并保存到指定路径，随后在另一应用中提交结果。</x:v>
+      </x:c>
+      <x:c r="G22" s="98" t="str">
+        <x:v>任务级 execution-based evaluator 检查文件、应用或网站真实状态，而不是依赖最后一段自然语言。</x:v>
+      </x:c>
+      <x:c r="H22" s="98" t="str">
+        <x:v>Setup、Contract、f_A、f_T、f_O、Budget；适合镜像状态、危险操作 guard、应用崩溃、视觉裁剪和长程预算。</x:v>
+      </x:c>
+      <x:c r="I22" s="98" t="str">
+        <x:v>作为成熟系统的高难外部有效性测试，覆盖本地 calendar/email 与 code/file 任务未包含的真实 GUI 噪声。</x:v>
+      </x:c>
+      <x:c r="J22" s="100" t="str">
+        <x:v>https://arxiv.org/abs/2606.29537</x:v>
+      </x:c>
+      <x:c r="K22" s="100" t="str">
+        <x:v>https://github.com/xlang-ai/OSWorld-V2</x:v>
+      </x:c>
+      <x:c r="L22" s="99" t="str">
+        <x:v>桌面长程压力测试</x:v>
+      </x:c>
+      <x:c r="M22" s="99" t="str">
+        <x:v>S14</x:v>
+      </x:c>
+      <x:c r="N22"/>
+      <x:c r="O22"/>
+      <x:c r="P22"/>
+      <x:c r="Q22"/>
+      <x:c r="R22"/>
+      <x:c r="S22"/>
+    </x:row>
+    <x:row r="23" ht="82" customHeight="1">
+      <x:c r="A23" s="99" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B19" s="76" t="n">
-        <x:f>SUM(K19:Q19)</x:f>
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C19" s="78" t="str">
-        <x:v>WebArena-Verified</x:v>
-      </x:c>
-      <x:c r="D19" s="78" t="str">
-        <x:v>Verified browser benchmark</x:v>
-      </x:c>
-      <x:c r="E19" s="78" t="str">
-        <x:v>03 issue workflow</x:v>
-      </x:c>
-      <x:c r="F19" s="78" t="str">
-        <x:v>多站点浏览器</x:v>
-      </x:c>
-      <x:c r="G19" s="78" t="str">
-        <x:v>BrowserGym / Playwright</x:v>
-      </x:c>
-      <x:c r="H19" s="78" t="str">
-        <x:v>GitLab 子集 10 个完全自托管任务</x:v>
-      </x:c>
-      <x:c r="I19" s="78" t="str">
-        <x:v>response + network trace evaluator</x:v>
-      </x:c>
-      <x:c r="J19" s="78" t="str">
-        <x:v>站点镜像/重建</x:v>
-      </x:c>
-      <x:c r="K19" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="L19" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="M19" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N19" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="O19" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="P19" s="76" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q19" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="R19" s="78" t="str">
-        <x:v>先实现可复用 BrowserGymAdapter；站点 reset 稳定后再进入主实验。</x:v>
-      </x:c>
-      <x:c r="S19" s="77" t="str">
-        <x:v>S36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="44" customHeight="1">
-      <x:c r="A20" s="76" t="str">
-        <x:f>IF(AND(B20&gt;=12,P20&gt;=1),"P0",IF(AND(B20&gt;=8,NOT(AND(M20&lt;=1,P20=0))),"P1","P2"))</x:f>
+      <x:c r="B23" s="98" t="str">
+        <x:v>OfficeQA</x:v>
+      </x:c>
+      <x:c r="C23" s="98" t="str">
+        <x:v>基于办公/金融文档的检索与问答 benchmark。它能评估 Agent 在长文档中搜索、引用和计算，但缺少持续可变的交互环境。</x:v>
+      </x:c>
+      <x:c r="D23" s="98" t="str">
+        <x:v>静态文档语料和问题；状态主要是检索上下文，而非由动作改变的业务世界。</x:v>
+      </x:c>
+      <x:c r="E23" s="98" t="str">
+        <x:v>文档搜索、页面读取、检索和回答；通常没有写副作用。</x:v>
+      </x:c>
+      <x:c r="F23" s="98" t="str">
+        <x:v>从年度报告中找到两个时期的指标并计算变化，回答时给出依据。</x:v>
+      </x:c>
+      <x:c r="G23" s="98" t="str">
+        <x:v>使用答案匹配、EM/F1 或任务定义的 QA evaluator；可检查检索是否支持最终答案。</x:v>
+      </x:c>
+      <x:c r="H23" s="98" t="str">
+        <x:v>以 f_O、Contract、Budget 为主；Setup/f_A/f_T 的研究空间较弱。</x:v>
+      </x:c>
+      <x:c r="I23" s="98" t="str">
+        <x:v>适合作为 observation-only 对照，证明改进信息可见性不等于完整的环境演化。</x:v>
+      </x:c>
+      <x:c r="J23" s="100" t="str">
+        <x:v>https://github.com/databricks/officeqa</x:v>
+      </x:c>
+      <x:c r="K23" s="100" t="str">
+        <x:v>https://github.com/databricks/officeqa</x:v>
+      </x:c>
+      <x:c r="L23" s="99" t="str">
+        <x:v>静态观察对照</x:v>
+      </x:c>
+      <x:c r="M23" s="99" t="str">
+        <x:v>S10</x:v>
+      </x:c>
+      <x:c r="N23"/>
+      <x:c r="O23"/>
+      <x:c r="P23"/>
+      <x:c r="Q23"/>
+      <x:c r="R23"/>
+      <x:c r="S23"/>
+    </x:row>
+    <x:row r="24" ht="82" customHeight="1">
+      <x:c r="A24" s="99" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B20" s="76" t="n">
-        <x:f>SUM(K20:Q20)</x:f>
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C20" s="78" t="str">
-        <x:v>WorkArena / WorkArena++</x:v>
-      </x:c>
-      <x:c r="D20" s="78" t="str">
-        <x:v>Enterprise web benchmark</x:v>
-      </x:c>
-      <x:c r="E20" s="78" t="str">
-        <x:v>03 issue workflow 的后期迁移</x:v>
-      </x:c>
-      <x:c r="F20" s="78" t="str">
-        <x:v>ServiceNow Web UI</x:v>
-      </x:c>
-      <x:c r="G20" s="78" t="str">
-        <x:v>BrowserGym actions</x:v>
-      </x:c>
-      <x:c r="H20" s="78" t="str">
-        <x:v>审批后选 10 个单工作流任务</x:v>
-      </x:c>
-      <x:c r="I20" s="78" t="str">
-        <x:v>程序化 task evaluator</x:v>
-      </x:c>
-      <x:c r="J20" s="78" t="str">
-        <x:v>实例 reset 成本高</x:v>
-      </x:c>
-      <x:c r="K20" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="L20" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="M20" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N20" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="O20" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="P20" s="76" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q20" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R20" s="78" t="str">
-        <x:v>复用 BrowserGymAdapter；部署和账号状态稳定性是前置门禁。</x:v>
-      </x:c>
-      <x:c r="S20" s="77" t="str">
-        <x:v>S08</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" ht="44" customHeight="1">
-      <x:c r="A21" s="76" t="str">
-        <x:f>IF(AND(B21&gt;=12,P21&gt;=1),"P0",IF(AND(B21&gt;=8,NOT(AND(M21&lt;=1,P21=0))),"P1","P2"))</x:f>
+      <x:c r="B24" s="98" t="str">
+        <x:v>SkillsBench</x:v>
+      </x:c>
+      <x:c r="C24" s="98" t="str">
+        <x:v>用于评价外部 skill/说明文档是否帮助 Agent 完成工具和文件任务的 benchmark。研究重点是 skill transfer，而不是环境本身如何被改变。</x:v>
+      </x:c>
+      <x:c r="D24" s="98" t="str">
+        <x:v>任务隔离的工具或文件状态；skill 作为额外上下文加载，环境通常保持固定。</x:v>
+      </x:c>
+      <x:c r="E24" s="98" t="str">
+        <x:v>任务特定工具与文件操作；Agent 可比较无 skill、人工 skill、轨迹生成 skill。</x:v>
+      </x:c>
+      <x:c r="F24" s="98" t="str">
+        <x:v>给 Agent 一份操作 skill，让它按约束修改文件或调用工具；比较是否减少错误步骤并通过 verifier。</x:v>
+      </x:c>
+      <x:c r="G24" s="98" t="str">
+        <x:v>任务确定性 verifier 检查最终产物；同时可记录 skill 使用和轨迹长度。</x:v>
+      </x:c>
+      <x:c r="H24" s="98" t="str">
+        <x:v>主要对应 Contract、f_O、Budget；更适合评估环境节点产出的知识，而非搜索环境节点。</x:v>
+      </x:c>
+      <x:c r="I24" s="98" t="str">
+        <x:v>第二阶段用于回答：环境修复成功后，能否压缩为可迁移 skill 并在原环境外发挥作用。</x:v>
+      </x:c>
+      <x:c r="J24" s="100" t="str">
+        <x:v>https://arxiv.org/abs/2602.12670</x:v>
+      </x:c>
+      <x:c r="K24" s="100" t="str">
+        <x:v>https://arxiv.org/abs/2602.12670</x:v>
+      </x:c>
+      <x:c r="L24" s="99" t="str">
+        <x:v>skill 迁移评估</x:v>
+      </x:c>
+      <x:c r="M24" s="99" t="str">
+        <x:v>S22</x:v>
+      </x:c>
+      <x:c r="N24"/>
+      <x:c r="O24"/>
+      <x:c r="P24"/>
+      <x:c r="Q24"/>
+      <x:c r="R24"/>
+      <x:c r="S24"/>
+    </x:row>
+    <x:row r="25" ht="82" customHeight="1">
+      <x:c r="A25" s="99" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B21" s="76" t="n">
-        <x:f>SUM(K21:Q21)</x:f>
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C21" s="78" t="str">
-        <x:v>AndroidWorld</x:v>
-      </x:c>
-      <x:c r="D21" s="78" t="str">
-        <x:v>Parameterized mobile benchmark</x:v>
-      </x:c>
-      <x:c r="E21" s="78" t="str">
-        <x:v>无直接本地场景</x:v>
-      </x:c>
-      <x:c r="F21" s="78" t="str">
-        <x:v>Android 模拟器</x:v>
-      </x:c>
-      <x:c r="G21" s="78" t="str">
-        <x:v>touch / text / app</x:v>
-      </x:c>
-      <x:c r="H21" s="78" t="str">
-        <x:v>单 app、确定性 setup/teardown 子集</x:v>
-      </x:c>
-      <x:c r="I21" s="78" t="str">
-        <x:v>setup/success/teardown</x:v>
-      </x:c>
-      <x:c r="J21" s="78" t="str">
-        <x:v>模拟器重置</x:v>
-      </x:c>
-      <x:c r="K21" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L21" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="M21" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N21" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="O21" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="P21" s="76" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q21" s="76" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R21" s="78" t="str">
-        <x:v>任务参数化值得借鉴，但设备运行时不进入第一轮实验。</x:v>
-      </x:c>
-      <x:c r="S21" s="77" t="str">
-        <x:v>S15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" ht="44" customHeight="1">
-      <x:c r="A22" s="76" t="str">
-        <x:f>IF(AND(B22&gt;=12,P22&gt;=1),"P0",IF(AND(B22&gt;=8,NOT(AND(M22&lt;=1,P22=0))),"P1","P2"))</x:f>
+      <x:c r="B25" s="98" t="str">
+        <x:v>LiveCodeBench</x:v>
+      </x:c>
+      <x:c r="C25" s="98" t="str">
+        <x:v>持续更新的新鲜编程题 benchmark，用时间切分降低训练数据污染。它主要测代码生成能力，缺少多轮、状态化的工具环境。</x:v>
+      </x:c>
+      <x:c r="D25" s="98" t="str">
+        <x:v>题目、输入输出规范和隐藏测试；提交之间通常不形成可继续操作的世界状态。</x:v>
+      </x:c>
+      <x:c r="E25" s="98" t="str">
+        <x:v>生成代码并提交；动作边界比 coding agent 的真实 repo 工具更窄。</x:v>
+      </x:c>
+      <x:c r="F25" s="98" t="str">
+        <x:v>实现一个近期发布的算法题，在隐藏测试和时间限制下通过。</x:v>
+      </x:c>
+      <x:c r="G25" s="98" t="str">
+        <x:v>隐藏测试、正确率和运行约束。</x:v>
+      </x:c>
+      <x:c r="H25" s="98" t="str">
+        <x:v>可研究 Contract、f_O、Budget；Setup/f_T 与真实副作用较弱。</x:v>
+      </x:c>
+      <x:c r="I25" s="98" t="str">
+        <x:v>可作为 code capability 与污染控制基线，但不适合作为环境 DAG 的主载体。</x:v>
+      </x:c>
+      <x:c r="J25" s="100" t="str">
+        <x:v>https://arxiv.org/abs/2403.07974</x:v>
+      </x:c>
+      <x:c r="K25" s="100" t="str">
+        <x:v>https://github.com/LiveCodeBench/LiveCodeBench</x:v>
+      </x:c>
+      <x:c r="L25" s="99" t="str">
+        <x:v>新鲜代码能力对照</x:v>
+      </x:c>
+      <x:c r="M25" s="99" t="str">
+        <x:v>S33</x:v>
+      </x:c>
+      <x:c r="N25"/>
+      <x:c r="O25"/>
+      <x:c r="P25"/>
+      <x:c r="Q25"/>
+      <x:c r="R25"/>
+      <x:c r="S25"/>
+    </x:row>
+    <x:row r="26" ht="82" customHeight="1">
+      <x:c r="A26" s="99" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B22" s="76" t="n">
-        <x:f>SUM(K22:Q22)</x:f>
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C22" s="78" t="str">
-        <x:v>OSWorld 2.1</x:v>
-      </x:c>
-      <x:c r="D22" s="78" t="str">
-        <x:v>Desktop stress test</x:v>
-      </x:c>
-      <x:c r="E22" s="78" t="str">
-        <x:v>04/05 的真实 GUI 迁移</x:v>
-      </x:c>
-      <x:c r="F22" s="78" t="str">
-        <x:v>桌面 OS</x:v>
-      </x:c>
-      <x:c r="G22" s="78" t="str">
-        <x:v>GUI / accessibility</x:v>
-      </x:c>
-      <x:c r="H22" s="78" t="str">
-        <x:v>最后接入少量无账号任务</x:v>
-      </x:c>
-      <x:c r="I22" s="78" t="str">
-        <x:v>任务级执行式 evaluator</x:v>
-      </x:c>
-      <x:c r="J22" s="78" t="str">
-        <x:v>VM/镜像恢复</x:v>
-      </x:c>
-      <x:c r="K22" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L22" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="M22" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N22" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="O22" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="P22" s="76" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q22" s="76" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R22" s="78" t="str">
-        <x:v>高成本、reset 噪声大；只用于成熟系统的外部有效性。</x:v>
-      </x:c>
-      <x:c r="S22" s="77" t="str">
-        <x:v>S14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" ht="44" customHeight="1">
-      <x:c r="A23" s="76" t="str">
-        <x:f>IF(AND(B23&gt;=12,P23&gt;=1),"P0",IF(AND(B23&gt;=8,NOT(AND(M23&lt;=1,P23=0))),"P1","P2"))</x:f>
+      <x:c r="B26" s="98" t="str">
+        <x:v>Polyglot</x:v>
+      </x:c>
+      <x:c r="C26" s="98" t="str">
+        <x:v>多语言真实仓库修复集合，常用于比较 coding agent 或 Agent-RSI 方法。它能扩大语言覆盖，但任务重心仍是 Agent 如何修代码。</x:v>
+      </x:c>
+      <x:c r="D26" s="98" t="str">
+        <x:v>不同语言仓库、构建系统与测试环境；每个任务隔离重建。</x:v>
+      </x:c>
+      <x:c r="E26" s="98" t="str">
+        <x:v>shell 与文件工具；动作空间和 SWE-bench 类似，但工具链更加异构。</x:v>
+      </x:c>
+      <x:c r="F26" s="98" t="str">
+        <x:v>在 Rust、Java 或 JavaScript 仓库中定位 issue，修改实现并通过原有测试。</x:v>
+      </x:c>
+      <x:c r="G26" s="98" t="str">
+        <x:v>仓库测试和任务专用验证。</x:v>
+      </x:c>
+      <x:c r="H26" s="98" t="str">
+        <x:v>Setup、Contract、f_A、f_O、Budget；f_T 可模拟构建/命令故障。</x:v>
+      </x:c>
+      <x:c r="I26" s="98" t="str">
+        <x:v>保留为 Agent 自进化与环境辅助的对照，后期验证环境策略是否跨语言复用。</x:v>
+      </x:c>
+      <x:c r="J26" s="100" t="str">
+        <x:v>https://arxiv.org/abs/2505.22954</x:v>
+      </x:c>
+      <x:c r="K26" s="100" t="str">
+        <x:v>https://arxiv.org/abs/2505.22954</x:v>
+      </x:c>
+      <x:c r="L26" s="99" t="str">
+        <x:v>Agent-RSI 对照</x:v>
+      </x:c>
+      <x:c r="M26" s="99" t="str">
+        <x:v>S19</x:v>
+      </x:c>
+      <x:c r="N26"/>
+      <x:c r="O26"/>
+      <x:c r="P26"/>
+      <x:c r="Q26"/>
+      <x:c r="R26"/>
+      <x:c r="S26"/>
+    </x:row>
+    <x:row r="27" ht="82" customHeight="1">
+      <x:c r="A27" s="99" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B23" s="76" t="n">
-        <x:f>SUM(K23:Q23)</x:f>
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C23" s="78" t="str">
-        <x:v>OfficeQA</x:v>
-      </x:c>
-      <x:c r="D23" s="78" t="str">
-        <x:v>Observation-only control</x:v>
-      </x:c>
-      <x:c r="E23" s="78" t="str">
-        <x:v>Diagnostic/Contract 对照</x:v>
-      </x:c>
-      <x:c r="F23" s="78" t="str">
-        <x:v>文档检索</x:v>
-      </x:c>
-      <x:c r="G23" s="78" t="str">
-        <x:v>search / retrieval</x:v>
-      </x:c>
-      <x:c r="H23" s="78" t="str">
-        <x:v>固定语料上的检索观察与预算实验</x:v>
-      </x:c>
-      <x:c r="I23" s="78" t="str">
-        <x:v>EM/F1</x:v>
-      </x:c>
-      <x:c r="J23" s="78" t="str">
-        <x:v>静态语料</x:v>
-      </x:c>
-      <x:c r="K23" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L23" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M23" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="N23" s="76" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O23" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P23" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="Q23" s="76" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R23" s="78" t="str">
-        <x:v>缺少交互状态，只用于证明观察辅助不等于完整环境演化。</x:v>
-      </x:c>
-      <x:c r="S23" s="77" t="str">
-        <x:v>S10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" ht="44" customHeight="1">
-      <x:c r="A24" s="76" t="str">
-        <x:f>IF(AND(B24&gt;=12,P24&gt;=1),"P0",IF(AND(B24&gt;=8,NOT(AND(M24&lt;=1,P24=0))),"P1","P2"))</x:f>
+      <x:c r="B27" s="98" t="str">
+        <x:v>AgentBench</x:v>
+      </x:c>
+      <x:c r="C27" s="98" t="str">
+        <x:v>覆盖操作系统、数据库、知识图谱、网页和游戏等多种交互环境的综合 benchmark。覆盖广，但不同子环境的 action、reset 和 verifier 不统一。</x:v>
+      </x:c>
+      <x:c r="D27" s="98" t="str">
+        <x:v>由多个独立子环境组成，各自有不同状态和初始化方式，难以共享同一个 mutation surface。</x:v>
+      </x:c>
+      <x:c r="E27" s="98" t="str">
+        <x:v>环境特定动作；需要为每个子环境单独适配。</x:v>
+      </x:c>
+      <x:c r="F27" s="98" t="str">
+        <x:v>在数据库子任务中编写查询，在操作系统子任务中完成文件操作，再分别由原生 evaluator 评分。</x:v>
+      </x:c>
+      <x:c r="G27" s="98" t="str">
+        <x:v>沿用各子环境原生指标，适合总体验证，不适合直接比较同一个环境变化。</x:v>
+      </x:c>
+      <x:c r="H27" s="98" t="str">
+        <x:v>理论上可覆盖六类，但需要逐环境定义，难以做干净消融。</x:v>
+      </x:c>
+      <x:c r="I27" s="98" t="str">
+        <x:v>适合 adapter 和 mutation registry 稳定后的广域泛化评估，不作为第一阶段搜索空间。</x:v>
+      </x:c>
+      <x:c r="J27" s="100" t="str">
+        <x:v>https://arxiv.org/abs/2308.03688</x:v>
+      </x:c>
+      <x:c r="K27" s="100" t="str">
+        <x:v>https://github.com/THUDM/AgentBench</x:v>
+      </x:c>
+      <x:c r="L27" s="99" t="str">
+        <x:v>广域后期评估</x:v>
+      </x:c>
+      <x:c r="M27" s="99" t="str">
+        <x:v>S12</x:v>
+      </x:c>
+      <x:c r="N27"/>
+      <x:c r="O27"/>
+      <x:c r="P27"/>
+      <x:c r="Q27"/>
+      <x:c r="R27"/>
+      <x:c r="S27"/>
+    </x:row>
+    <x:row r="28" ht="82" customHeight="1">
+      <x:c r="A28" s="99" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B24" s="76" t="n">
-        <x:f>SUM(K24:Q24)</x:f>
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C24" s="78" t="str">
-        <x:v>SkillsBench</x:v>
-      </x:c>
-      <x:c r="D24" s="78" t="str">
-        <x:v>Skill transfer evaluation</x:v>
-      </x:c>
-      <x:c r="E24" s="78" t="str">
-        <x:v>JSON skill 加载链路</x:v>
-      </x:c>
-      <x:c r="F24" s="78" t="str">
-        <x:v>工具/文件任务</x:v>
-      </x:c>
-      <x:c r="G24" s="78" t="str">
-        <x:v>task-specific tools</x:v>
-      </x:c>
-      <x:c r="H24" s="78" t="str">
-        <x:v>评估环境轨迹生成 skill 的零样本迁移</x:v>
-      </x:c>
-      <x:c r="I24" s="78" t="str">
-        <x:v>确定性 verifier</x:v>
-      </x:c>
-      <x:c r="J24" s="78" t="str">
-        <x:v>任务隔离</x:v>
-      </x:c>
-      <x:c r="K24" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L24" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="M24" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N24" s="76" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O24" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P24" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q24" s="76" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R24" s="78" t="str">
-        <x:v>适合第二阶段评价 skill，不作为环境节点搜索底座。</x:v>
-      </x:c>
-      <x:c r="S24" s="77" t="str">
-        <x:v>S22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" ht="44" customHeight="1">
-      <x:c r="A25" s="76" t="str">
-        <x:f>IF(AND(B25&gt;=12,P25&gt;=1),"P0",IF(AND(B25&gt;=8,NOT(AND(M25&lt;=1,P25=0))),"P1","P2"))</x:f>
+      <x:c r="B28" s="98" t="str">
+        <x:v>AgentBoard</x:v>
+      </x:c>
+      <x:c r="C28" s="98" t="str">
+        <x:v>跨 benchmark 的分析与评测框架，强调细粒度 progress rate，帮助识别 Agent 在任务哪一步失败。它更接近诊断层，而不是一个可改变的环境。</x:v>
+      </x:c>
+      <x:c r="D28" s="98" t="str">
+        <x:v>依赖底层 benchmark 的状态；自身主要聚合轨迹、里程碑和评测结果。</x:v>
+      </x:c>
+      <x:c r="E28" s="98" t="str">
+        <x:v>evaluation adapters，而非独立的 Agent action space。</x:v>
+      </x:c>
+      <x:c r="F28" s="98" t="str">
+        <x:v>即使最终任务失败，也根据已完成的子目标计算进度，区分完全没开始与接近完成。</x:v>
+      </x:c>
+      <x:c r="G28" s="98" t="str">
+        <x:v>终局成功率 + progress rate 等过程指标。</x:v>
+      </x:c>
+      <x:c r="H28" s="98" t="str">
+        <x:v>不直接承载六类变化；可为 Diagnostic Agent 提供选点信号。</x:v>
+      </x:c>
+      <x:c r="I28" s="98" t="str">
+        <x:v>借鉴诊断指标，用于决定在环境 DAG 的哪个失败节点生成候选变化。</x:v>
+      </x:c>
+      <x:c r="J28" s="100" t="str">
+        <x:v>https://arxiv.org/abs/2401.13178</x:v>
+      </x:c>
+      <x:c r="K28" s="100" t="str">
+        <x:v>https://github.com/hkust-nlp/AgentBoard</x:v>
+      </x:c>
+      <x:c r="L28" s="99" t="str">
+        <x:v>诊断指标参考</x:v>
+      </x:c>
+      <x:c r="M28" s="99" t="str">
+        <x:v>S13</x:v>
+      </x:c>
+      <x:c r="N28"/>
+      <x:c r="O28"/>
+      <x:c r="P28"/>
+      <x:c r="Q28"/>
+      <x:c r="R28"/>
+      <x:c r="S28"/>
+    </x:row>
+    <x:row r="29" ht="82" customHeight="1">
+      <x:c r="A29" s="99" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B25" s="76" t="n">
-        <x:f>SUM(K25:Q25)</x:f>
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C25" s="78" t="str">
-        <x:v>LiveCodeBench</x:v>
-      </x:c>
-      <x:c r="D25" s="78" t="str">
-        <x:v>Fresh-code control</x:v>
-      </x:c>
-      <x:c r="E25" s="78" t="str">
-        <x:v>05 code repair 的污染对照</x:v>
-      </x:c>
-      <x:c r="F25" s="78" t="str">
-        <x:v>代码题</x:v>
-      </x:c>
-      <x:c r="G25" s="78" t="str">
-        <x:v>code submission</x:v>
-      </x:c>
-      <x:c r="H25" s="78" t="str">
-        <x:v>只测新鲜代码能力，不做环境 DAG</x:v>
-      </x:c>
-      <x:c r="I25" s="78" t="str">
-        <x:v>隐藏测试</x:v>
-      </x:c>
-      <x:c r="J25" s="78" t="str">
-        <x:v>无状态任务</x:v>
-      </x:c>
-      <x:c r="K25" s="76" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L25" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="M25" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="N25" s="76" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O25" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P25" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="Q25" s="76" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R25" s="78" t="str">
-        <x:v>可控制污染，但缺少多轮状态和可修改环境边界。</x:v>
-      </x:c>
-      <x:c r="S25" s="77" t="str">
-        <x:v>S33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" ht="44" customHeight="1">
-      <x:c r="A26" s="76" t="str">
-        <x:f>IF(AND(B26&gt;=12,P26&gt;=1),"P0",IF(AND(B26&gt;=8,NOT(AND(M26&lt;=1,P26=0))),"P1","P2"))</x:f>
+      <x:c r="B29" s="98" t="str">
+        <x:v>Procgen</x:v>
+      </x:c>
+      <x:c r="C29" s="98" t="str">
+        <x:v>程序生成游戏关卡套件，强调在训练关卡之外的 unseen levels 上泛化。它适合高吞吐课程学习，但 action/side-effect 语义与工具 Agent 差异较大。</x:v>
+      </x:c>
+      <x:c r="D29" s="98" t="str">
+        <x:v>由随机 seed 生成关卡状态，可快速 reset；状态通常为视觉帧和游戏内部变量。</x:v>
+      </x:c>
+      <x:c r="E29" s="98" t="str">
+        <x:v>离散控制动作，如移动、跳跃、交互。</x:v>
+      </x:c>
+      <x:c r="F29" s="98" t="str">
+        <x:v>在有限训练 seed 上学习后，进入未见过的 CoinRun 关卡并保持回报。</x:v>
+      </x:c>
+      <x:c r="G29" s="98" t="str">
+        <x:v>episode return 与关卡完成率。</x:v>
+      </x:c>
+      <x:c r="H29" s="98" t="str">
+        <x:v>主要对应 Setup、f_T、f_O、Budget；Contract 与业务工具 schema 不直接对应。</x:v>
+      </x:c>
+      <x:c r="I29" s="98" t="str">
+        <x:v>作为 procedural curriculum 和泛化控制参考，不作为当前工具环境的主 benchmark。</x:v>
+      </x:c>
+      <x:c r="J29" s="100" t="str">
+        <x:v>https://arxiv.org/abs/1912.01588</x:v>
+      </x:c>
+      <x:c r="K29" s="100" t="str">
+        <x:v>https://github.com/openai/procgen</x:v>
+      </x:c>
+      <x:c r="L29" s="99" t="str">
+        <x:v>程序生成控制参考</x:v>
+      </x:c>
+      <x:c r="M29" s="99" t="str">
+        <x:v>S25</x:v>
+      </x:c>
+      <x:c r="N29"/>
+      <x:c r="O29"/>
+      <x:c r="P29"/>
+      <x:c r="Q29"/>
+      <x:c r="R29"/>
+      <x:c r="S29"/>
+    </x:row>
+    <x:row r="30" ht="82" customHeight="1">
+      <x:c r="A30" s="99" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B26" s="76" t="n">
-        <x:f>SUM(K26:Q26)</x:f>
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C26" s="78" t="str">
-        <x:v>Polyglot</x:v>
-      </x:c>
-      <x:c r="D26" s="78" t="str">
-        <x:v>Agent-RSI comparison</x:v>
-      </x:c>
-      <x:c r="E26" s="78" t="str">
-        <x:v>05 code repair</x:v>
-      </x:c>
-      <x:c r="F26" s="78" t="str">
-        <x:v>多语言代码修复</x:v>
-      </x:c>
-      <x:c r="G26" s="78" t="str">
-        <x:v>shell + file tools</x:v>
-      </x:c>
-      <x:c r="H26" s="78" t="str">
-        <x:v>比较 Agent 自进化与环境辅助</x:v>
-      </x:c>
-      <x:c r="I26" s="78" t="str">
-        <x:v>测试</x:v>
-      </x:c>
-      <x:c r="J26" s="78" t="str">
-        <x:v>任务隔离</x:v>
-      </x:c>
-      <x:c r="K26" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L26" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="M26" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N26" s="76" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O26" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P26" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q26" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R26" s="78" t="str">
-        <x:v>保留为 Agent RSI 对照，不进入首轮环境搜索。</x:v>
-      </x:c>
-      <x:c r="S26" s="77" t="str">
-        <x:v>S19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" ht="44" customHeight="1">
-      <x:c r="A27" s="76" t="str">
-        <x:f>IF(AND(B27&gt;=12,P27&gt;=1),"P0",IF(AND(B27&gt;=8,NOT(AND(M27&lt;=1,P27=0))),"P1","P2"))</x:f>
+      <x:c r="B30" s="98" t="str">
+        <x:v>PAIRED testbeds</x:v>
+      </x:c>
+      <x:c r="C30" s="98" t="str">
+        <x:v>Unsupervised Environment Design 方法：teacher 生成关卡，使 antagonist 与 protagonist 的回报差（regret）增大，从而寻找困难但可能可解的环境。</x:v>
+      </x:c>
+      <x:c r="D30" s="98" t="str">
+        <x:v>程序化迷宫或控制环境；teacher 的动作改变关卡结构，两个 learner 在同一关卡上评估。</x:v>
+      </x:c>
+      <x:c r="E30" s="98" t="str">
+        <x:v>环境生成动作 + learner 控制动作。</x:v>
+      </x:c>
+      <x:c r="F30" s="98" t="str">
+        <x:v>teacher 生成迷宫；antagonist 能到达目标而 protagonist 失败时 regret 高，该关卡被用于训练 protagonist。</x:v>
+      </x:c>
+      <x:c r="G30" s="98" t="str">
+        <x:v>episode return、regret 与可解性信号。</x:v>
+      </x:c>
+      <x:c r="H30" s="98" t="str">
+        <x:v>主要启发 Setup/f_T 的候选生成与 selection；不直接提供工具契约或副作用模型。</x:v>
+      </x:c>
+      <x:c r="I30" s="98" t="str">
+        <x:v>借鉴“困难但可解”的选择目标，但本项目用固定 Target 的成功率差和父节点回测替代双 Agent regret。</x:v>
+      </x:c>
+      <x:c r="J30" s="100" t="str">
+        <x:v>https://papers.nips.cc/paper/2020/hash/985e9a46e10005356bbaf194249f6856-Abstract.html</x:v>
+      </x:c>
+      <x:c r="K30" s="100" t="str">
+        <x:v>https://papers.nips.cc/paper/2020/hash/985e9a46e10005356bbaf194249f6856-Abstract.html</x:v>
+      </x:c>
+      <x:c r="L30" s="99" t="str">
+        <x:v>环境设计理论参考</x:v>
+      </x:c>
+      <x:c r="M30" s="99" t="str">
+        <x:v>S23</x:v>
+      </x:c>
+      <x:c r="N30"/>
+      <x:c r="O30"/>
+      <x:c r="P30"/>
+      <x:c r="Q30"/>
+      <x:c r="R30"/>
+      <x:c r="S30"/>
+    </x:row>
+    <x:row r="31" ht="82" customHeight="1">
+      <x:c r="A31" s="99" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B27" s="76" t="n">
-        <x:f>SUM(K27:Q27)</x:f>
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C27" s="78" t="str">
-        <x:v>AgentBench</x:v>
-      </x:c>
-      <x:c r="D27" s="78" t="str">
-        <x:v>Broad late evaluation</x:v>
-      </x:c>
-      <x:c r="E27" s="78" t="str">
-        <x:v>统一 Agent 接口</x:v>
-      </x:c>
-      <x:c r="F27" s="78" t="str">
-        <x:v>八类交互环境</x:v>
-      </x:c>
-      <x:c r="G27" s="78" t="str">
-        <x:v>environment-specific</x:v>
-      </x:c>
-      <x:c r="H27" s="78" t="str">
-        <x:v>只在 adapter 稳定后做泛化评测</x:v>
-      </x:c>
-      <x:c r="I27" s="78" t="str">
-        <x:v>子环境原生指标</x:v>
-      </x:c>
-      <x:c r="J27" s="78" t="str">
-        <x:v>各子环境不同</x:v>
-      </x:c>
-      <x:c r="K27" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L27" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M27" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N27" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O27" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P27" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q27" s="76" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R27" s="78" t="str">
-        <x:v>覆盖广但无法共享一致快照与 mutation surface。</x:v>
-      </x:c>
-      <x:c r="S27" s="77" t="str">
-        <x:v>S12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" ht="44" customHeight="1">
-      <x:c r="A28" s="76" t="str">
-        <x:f>IF(AND(B28&gt;=12,P28&gt;=1),"P0",IF(AND(B28&gt;=8,NOT(AND(M28&lt;=1,P28=0))),"P1","P2"))</x:f>
+      <x:c r="B31" s="98" t="str">
+        <x:v>ACCEL testbeds</x:v>
+      </x:c>
+      <x:c r="C31" s="98" t="str">
+        <x:v>从已有可解关卡出发，通过局部编辑产生新关卡，并根据 regret/学习价值维护 replay buffer；比从零生成更接近本项目的 MutationSpec。</x:v>
+      </x:c>
+      <x:c r="D31" s="98" t="str">
+        <x:v>MiniGrid 或连续控制关卡；状态由可编辑的 level encoding 与 Agent rollout 组成。</x:v>
+      </x:c>
+      <x:c r="E31" s="98" t="str">
+        <x:v>局部 level editor + learner actions。</x:v>
+      </x:c>
+      <x:c r="F31" s="98" t="str">
+        <x:v>移动一堵墙或目标位置，产生只比父关卡难一点的子关卡；保留高学习价值样本并反复回放。</x:v>
+      </x:c>
+      <x:c r="G31" s="98" t="str">
+        <x:v>regret、return 和 replay priority。</x:v>
+      </x:c>
+      <x:c r="H31" s="98" t="str">
+        <x:v>主要启发 Setup/f_T 的单步局部变异、父子关系和 replay；工具环境仍需额外 Contract/f_A/f_O 定义。</x:v>
+      </x:c>
+      <x:c r="I31" s="98" t="str">
+        <x:v>是环境 DAG 搜索策略最直接的理论参考：一次只改一个可解释维度，并保留父节点作为回归基线。</x:v>
+      </x:c>
+      <x:c r="J31" s="100" t="str">
+        <x:v>https://proceedings.mlr.press/v162/parker-holder22a.html</x:v>
+      </x:c>
+      <x:c r="K31" s="100" t="str">
+        <x:v>https://proceedings.mlr.press/v162/parker-holder22a.html</x:v>
+      </x:c>
+      <x:c r="L31" s="99" t="str">
+        <x:v>局部环境编辑参考</x:v>
+      </x:c>
+      <x:c r="M31" s="99" t="str">
+        <x:v>S24</x:v>
+      </x:c>
+      <x:c r="N31"/>
+      <x:c r="O31"/>
+      <x:c r="P31"/>
+      <x:c r="Q31"/>
+      <x:c r="R31"/>
+      <x:c r="S31"/>
+    </x:row>
+    <x:row r="32" ht="82" customHeight="1">
+      <x:c r="A32" s="99" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B28" s="76" t="n">
-        <x:f>SUM(K28:Q28)</x:f>
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C28" s="78" t="str">
-        <x:v>AgentBoard</x:v>
-      </x:c>
-      <x:c r="D28" s="78" t="str">
-        <x:v>Diagnostic metric reference</x:v>
-      </x:c>
-      <x:c r="E28" s="78" t="str">
-        <x:v>Diagnostic Agent</x:v>
-      </x:c>
-      <x:c r="F28" s="78" t="str">
-        <x:v>多 benchmark 评测层</x:v>
-      </x:c>
-      <x:c r="G28" s="78" t="str">
-        <x:v>evaluation adapters</x:v>
-      </x:c>
-      <x:c r="H28" s="78" t="str">
-        <x:v>借鉴 progress rate，不接为环境</x:v>
-      </x:c>
-      <x:c r="I28" s="78" t="str">
-        <x:v>终局 + progress rate</x:v>
-      </x:c>
-      <x:c r="J28" s="78" t="str">
-        <x:v>依赖底层环境</x:v>
-      </x:c>
-      <x:c r="K28" s="76" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L28" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M28" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N28" s="76" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O28" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="P28" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="Q28" s="76" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R28" s="78" t="str">
-        <x:v>用于设计过程指标，而不是生成环境节点。</x:v>
-      </x:c>
-      <x:c r="S28" s="77" t="str">
-        <x:v>S13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" ht="44" customHeight="1">
-      <x:c r="A29" s="76" t="str">
-        <x:f>IF(AND(B29&gt;=12,P29&gt;=1),"P0",IF(AND(B29&gt;=8,NOT(AND(M29&lt;=1,P29=0))),"P1","P2"))</x:f>
+      <x:c r="B32" s="98" t="str">
+        <x:v>Factorio</x:v>
+      </x:c>
+      <x:c r="C32" s="98" t="str">
+        <x:v>开放式、长程建造环境，Agent 需要采集资源、研究技术并构建生产链。任务持续时间长、状态巨大，适合研究长期进步而非快速候选验证。</x:v>
+      </x:c>
+      <x:c r="D32" s="98" t="str">
+        <x:v>持久游戏世界、库存、机器、配方和空间布局；可通过存档恢复。</x:v>
+      </x:c>
+      <x:c r="E32" s="98" t="str">
+        <x:v>游戏 API、代码或控制动作。</x:v>
+      </x:c>
+      <x:c r="F32" s="98" t="str">
+        <x:v>从基础资源开始建立自动化冶炼和科研流水线，逐步解锁更高级目标。</x:v>
+      </x:c>
+      <x:c r="G32" s="98" t="str">
+        <x:v>里程碑、产量和技术进度；通常比单一业务 verifier 更开放。</x:v>
+      </x:c>
+      <x:c r="H32" s="98" t="str">
+        <x:v>可研究 Setup、Contract、f_A、f_T、f_O、Budget，但变化的语义边界更难固定。</x:v>
+      </x:c>
+      <x:c r="I32" s="98" t="str">
+        <x:v>作为长程、开放式环境参考；不适合早期做大量可重复环境节点实验。</x:v>
+      </x:c>
+      <x:c r="J32" s="100" t="str">
+        <x:v>https://arxiv.org/abs/2608.23552</x:v>
+      </x:c>
+      <x:c r="K32" s="100" t="str">
+        <x:v>https://arxiv.org/abs/2608.23552</x:v>
+      </x:c>
+      <x:c r="L32" s="99" t="str">
+        <x:v>长程开放环境参考</x:v>
+      </x:c>
+      <x:c r="M32" s="99" t="str">
+        <x:v>S18</x:v>
+      </x:c>
+      <x:c r="N32"/>
+      <x:c r="O32"/>
+      <x:c r="P32"/>
+      <x:c r="Q32"/>
+      <x:c r="R32"/>
+      <x:c r="S32"/>
+    </x:row>
+    <x:row r="33" ht="82" customHeight="1">
+      <x:c r="A33" s="99" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B29" s="76" t="n">
-        <x:f>SUM(K29:Q29)</x:f>
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C29" s="78" t="str">
-        <x:v>Procgen</x:v>
-      </x:c>
-      <x:c r="D29" s="78" t="str">
-        <x:v>Procedural control reference</x:v>
-      </x:c>
-      <x:c r="E29" s="78" t="str">
-        <x:v>无直接本地场景</x:v>
-      </x:c>
-      <x:c r="F29" s="78" t="str">
-        <x:v>程序化游戏</x:v>
-      </x:c>
-      <x:c r="G29" s="78" t="str">
-        <x:v>discrete control</x:v>
-      </x:c>
-      <x:c r="H29" s="78" t="str">
-        <x:v>只作为随机课程基线参考</x:v>
-      </x:c>
-      <x:c r="I29" s="78" t="str">
-        <x:v>游戏回报</x:v>
-      </x:c>
-      <x:c r="J29" s="78" t="str">
-        <x:v>seed reset</x:v>
-      </x:c>
-      <x:c r="K29" s="76" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L29" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M29" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="N29" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O29" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P29" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="Q29" s="76" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R29" s="78" t="str">
-        <x:v>吞吐高但与工具 Agent 的 action/side effect 语义不同。</x:v>
-      </x:c>
-      <x:c r="S29" s="77" t="str">
-        <x:v>S25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" ht="44" customHeight="1">
-      <x:c r="A30" s="76" t="str">
-        <x:f>IF(AND(B30&gt;=12,P30&gt;=1),"P0",IF(AND(B30&gt;=8,NOT(AND(M30&lt;=1,P30=0))),"P1","P2"))</x:f>
+      <x:c r="B33" s="98" t="str">
+        <x:v>POET / BipedalWalker</x:v>
+      </x:c>
+      <x:c r="C33" s="98" t="str">
+        <x:v>同时维护环境与策略种群的开放式进化方法。新环境需满足 minimal criterion，并允许不同策略在环境之间迁移。</x:v>
+      </x:c>
+      <x:c r="D33" s="98" t="str">
+        <x:v>连续控制地形与对应策略档案；环境参数可程序化变异。</x:v>
+      </x:c>
+      <x:c r="E33" s="98" t="str">
+        <x:v>连续控制动作 + 地形 mutation。</x:v>
+      </x:c>
+      <x:c r="F33" s="98" t="str">
+        <x:v>从简单地形出发逐步增加坡度、障碍或间距；当现有策略仍有机会解决时保留新环境。</x:v>
+      </x:c>
+      <x:c r="G33" s="98" t="str">
+        <x:v>环境回报、minimal criterion、novelty 和跨环境 transfer。</x:v>
+      </x:c>
+      <x:c r="H33" s="98" t="str">
+        <x:v>主要启发 Setup/f_T 与 EnvironmentDAG archive；Contract/f_A/f_O 不是其核心。</x:v>
+      </x:c>
+      <x:c r="I33" s="98" t="str">
+        <x:v>借鉴环境档案与跨节点迁移，但不复制昂贵的环境—策略共同进化循环。</x:v>
+      </x:c>
+      <x:c r="J33" s="100" t="str">
+        <x:v>https://proceedings.mlr.press/v119/wang20l.html</x:v>
+      </x:c>
+      <x:c r="K33" s="100" t="str">
+        <x:v>https://proceedings.mlr.press/v119/wang20l.html</x:v>
+      </x:c>
+      <x:c r="L33" s="99" t="str">
+        <x:v>开放式环境档案参考</x:v>
+      </x:c>
+      <x:c r="M33" s="99" t="str">
+        <x:v>S26</x:v>
+      </x:c>
+      <x:c r="N33"/>
+      <x:c r="O33"/>
+      <x:c r="P33"/>
+      <x:c r="Q33"/>
+      <x:c r="R33"/>
+      <x:c r="S33"/>
+    </x:row>
+    <x:row r="34" ht="82" customHeight="1">
+      <x:c r="A34" s="99" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B30" s="76" t="n">
-        <x:f>SUM(K30:Q30)</x:f>
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C30" s="78" t="str">
-        <x:v>PAIRED testbeds</x:v>
-      </x:c>
-      <x:c r="D30" s="78" t="str">
-        <x:v>UED theory reference</x:v>
-      </x:c>
-      <x:c r="E30" s="78" t="str">
-        <x:v>Diagnostic→candidate 的理论对照</x:v>
-      </x:c>
-      <x:c r="F30" s="78" t="str">
-        <x:v>迷宫/控制</x:v>
-      </x:c>
-      <x:c r="G30" s="78" t="str">
-        <x:v>teacher + agents</x:v>
-      </x:c>
-      <x:c r="H30" s="78" t="str">
-        <x:v>不进入主 benchmark 运行矩阵</x:v>
-      </x:c>
-      <x:c r="I30" s="78" t="str">
-        <x:v>回报 + regret</x:v>
-      </x:c>
-      <x:c r="J30" s="78" t="str">
-        <x:v>程序化重置</x:v>
-      </x:c>
-      <x:c r="K30" s="76" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L30" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M30" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="N30" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O30" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P30" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q30" s="76" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R30" s="78" t="str">
-        <x:v>借鉴困难但可解的 selection signal，不复刻三方训练。</x:v>
-      </x:c>
-      <x:c r="S30" s="77" t="str">
-        <x:v>S23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" ht="44" customHeight="1">
-      <x:c r="A31" s="76" t="str">
-        <x:f>IF(AND(B31&gt;=12,P31&gt;=1),"P0",IF(AND(B31&gt;=8,NOT(AND(M31&lt;=1,P31=0))),"P1","P2"))</x:f>
+      <x:c r="B34" s="98" t="str">
+        <x:v>OMNI-EPIC</x:v>
+      </x:c>
+      <x:c r="C34" s="98" t="str">
+        <x:v>利用 foundation model 生成新任务、模拟器代码或奖励的开放式环境生成工作，代表环境演化的高自由度上界。</x:v>
+      </x:c>
+      <x:c r="D34" s="98" t="str">
+        <x:v>生成的模拟环境、任务描述、奖励代码和 Agent rollout；环境语义可能随代码生成大幅变化。</x:v>
+      </x:c>
+      <x:c r="E34" s="98" t="str">
+        <x:v>生成器修改 simulator/reward，Agent 再在新环境中行动。</x:v>
+      </x:c>
+      <x:c r="F34" s="98" t="str">
+        <x:v>模型生成一个新的物理挑战及其 reward function，再通过 Agent 训练结果决定是否保留。</x:v>
+      </x:c>
+      <x:c r="G34" s="98" t="str">
+        <x:v>生成奖励、可执行性、Agent 表现和新颖性。</x:v>
+      </x:c>
+      <x:c r="H34" s="98" t="str">
+        <x:v>可覆盖 Setup/f_T/f_O，甚至重写整个环境；但难以保持 verifier 和任务语义不变。</x:v>
+      </x:c>
+      <x:c r="I34" s="98" t="str">
+        <x:v>作为未来开放式方向；当前项目应先限制 MutationSpec，避免生成任意代码导致不可解释的成功。</x:v>
+      </x:c>
+      <x:c r="J34" s="100" t="str">
+        <x:v>https://arxiv.org/abs/2405.15568</x:v>
+      </x:c>
+      <x:c r="K34" s="100" t="str">
+        <x:v>https://arxiv.org/abs/2405.15568</x:v>
+      </x:c>
+      <x:c r="L34" s="99" t="str">
+        <x:v>开放式生成上界</x:v>
+      </x:c>
+      <x:c r="M34" s="99" t="str">
+        <x:v>S27</x:v>
+      </x:c>
+      <x:c r="N34"/>
+      <x:c r="O34"/>
+      <x:c r="P34"/>
+      <x:c r="Q34"/>
+      <x:c r="R34"/>
+      <x:c r="S34"/>
+    </x:row>
+    <x:row r="35" ht="82" customHeight="1">
+      <x:c r="A35" s="99" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B31" s="76" t="n">
-        <x:f>SUM(K31:Q31)</x:f>
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C31" s="78" t="str">
-        <x:v>ACCEL testbeds</x:v>
-      </x:c>
-      <x:c r="D31" s="78" t="str">
-        <x:v>Search theory reference</x:v>
-      </x:c>
-      <x:c r="E31" s="78" t="str">
-        <x:v>MutationSpec + EnvironmentDAG</x:v>
-      </x:c>
-      <x:c r="F31" s="78" t="str">
-        <x:v>MiniGrid/控制</x:v>
-      </x:c>
-      <x:c r="G31" s="78" t="str">
-        <x:v>level editor</x:v>
-      </x:c>
-      <x:c r="H31" s="78" t="str">
-        <x:v>用于定义局部变异基线</x:v>
-      </x:c>
-      <x:c r="I31" s="78" t="str">
-        <x:v>regret / reward</x:v>
-      </x:c>
-      <x:c r="J31" s="78" t="str">
-        <x:v>程序化重置</x:v>
-      </x:c>
-      <x:c r="K31" s="76" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L31" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M31" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="N31" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O31" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P31" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q31" s="76" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R31" s="78" t="str">
-        <x:v>最接近局部编辑思想，但原 level 编码不能直接迁移到工具环境。</x:v>
-      </x:c>
-      <x:c r="S31" s="77" t="str">
-        <x:v>S24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" ht="44" customHeight="1">
-      <x:c r="A32" s="76" t="str">
-        <x:f>IF(AND(B32&gt;=12,P32&gt;=1),"P0",IF(AND(B32&gt;=8,NOT(AND(M32&lt;=1,P32=0))),"P1","P2"))</x:f>
-        <x:v>P2</x:v>
-      </x:c>
-      <x:c r="B32" s="76" t="n">
-        <x:f>SUM(K32:Q32)</x:f>
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C32" s="78" t="str">
-        <x:v>Factorio</x:v>
-      </x:c>
-      <x:c r="D32" s="78" t="str">
-        <x:v>Long-horizon reference</x:v>
-      </x:c>
-      <x:c r="E32" s="78" t="str">
-        <x:v>无直接本地场景</x:v>
-      </x:c>
-      <x:c r="F32" s="78" t="str">
-        <x:v>开放式游戏</x:v>
-      </x:c>
-      <x:c r="G32" s="78" t="str">
-        <x:v>game API / code</x:v>
-      </x:c>
-      <x:c r="H32" s="78" t="str">
-        <x:v>仅保留为长期性参考</x:v>
-      </x:c>
-      <x:c r="I32" s="78" t="str">
-        <x:v>进度指标</x:v>
-      </x:c>
-      <x:c r="J32" s="78" t="str">
-        <x:v>世界存档</x:v>
-      </x:c>
-      <x:c r="K32" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L32" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M32" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N32" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O32" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P32" s="76" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q32" s="76" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R32" s="78" t="str">
-        <x:v>任务长且 verifier 较弱，不适合快速环境候选验证。</x:v>
-      </x:c>
-      <x:c r="S32" s="77" t="str">
-        <x:v>S18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" ht="44" customHeight="1">
-      <x:c r="A33" s="76" t="str">
-        <x:f>IF(AND(B33&gt;=12,P33&gt;=1),"P0",IF(AND(B33&gt;=8,NOT(AND(M33&lt;=1,P33=0))),"P1","P2"))</x:f>
-        <x:v>P2</x:v>
-      </x:c>
-      <x:c r="B33" s="76" t="n">
-        <x:f>SUM(K33:Q33)</x:f>
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C33" s="78" t="str">
-        <x:v>POET BipedalWalker</x:v>
-      </x:c>
-      <x:c r="D33" s="78" t="str">
-        <x:v>Archive theory reference</x:v>
-      </x:c>
-      <x:c r="E33" s="78" t="str">
-        <x:v>EnvironmentDAG</x:v>
-      </x:c>
-      <x:c r="F33" s="78" t="str">
-        <x:v>连续控制</x:v>
-      </x:c>
-      <x:c r="G33" s="78" t="str">
-        <x:v>continuous control</x:v>
-      </x:c>
-      <x:c r="H33" s="78" t="str">
-        <x:v>只借鉴档案与迁移</x:v>
-      </x:c>
-      <x:c r="I33" s="78" t="str">
-        <x:v>回报 + minimal criterion</x:v>
-      </x:c>
-      <x:c r="J33" s="78" t="str">
-        <x:v>程序化重置</x:v>
-      </x:c>
-      <x:c r="K33" s="76" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L33" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M33" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="N33" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O33" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P33" s="76" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q33" s="76" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R33" s="78" t="str">
-        <x:v>环境—策略配对计算昂贵且域特定。</x:v>
-      </x:c>
-      <x:c r="S33" s="77" t="str">
-        <x:v>S26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" ht="44" customHeight="1">
-      <x:c r="A34" s="76" t="str">
-        <x:f>IF(AND(B34&gt;=12,P34&gt;=1),"P0",IF(AND(B34&gt;=8,NOT(AND(M34&lt;=1,P34=0))),"P1","P2"))</x:f>
-        <x:v>P2</x:v>
-      </x:c>
-      <x:c r="B34" s="76" t="n">
-        <x:f>SUM(K34:Q34)</x:f>
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C34" s="78" t="str">
-        <x:v>OMNI-EPIC</x:v>
-      </x:c>
-      <x:c r="D34" s="78" t="str">
-        <x:v>Open-ended future work</x:v>
-      </x:c>
-      <x:c r="E34" s="78" t="str">
-        <x:v>MutationSpec 的开放式上界</x:v>
-      </x:c>
-      <x:c r="F34" s="78" t="str">
-        <x:v>生成物理环境</x:v>
-      </x:c>
-      <x:c r="G34" s="78" t="str">
-        <x:v>generated simulator</x:v>
-      </x:c>
-      <x:c r="H34" s="78" t="str">
-        <x:v>不进入当前路线</x:v>
-      </x:c>
-      <x:c r="I34" s="78" t="str">
-        <x:v>生成奖励 + Agent 表现</x:v>
-      </x:c>
-      <x:c r="J34" s="78" t="str">
-        <x:v>仿真重置</x:v>
-      </x:c>
-      <x:c r="K34" s="76" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L34" s="76" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M34" s="76" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="N34" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O34" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P34" s="76" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q34" s="76" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R34" s="78" t="str">
-        <x:v>任意代码与奖励生成会破坏 verifier 不变性和安全边界。</x:v>
-      </x:c>
-      <x:c r="S34" s="77" t="str">
-        <x:v>S27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" ht="44" customHeight="1">
-      <x:c r="A35" s="76" t="str">
-        <x:f>IF(AND(B35&gt;=12,P35&gt;=1),"P0",IF(AND(B35&gt;=8,NOT(AND(M35&lt;=1,P35=0))),"P1","P2"))</x:f>
-        <x:v>P2</x:v>
-      </x:c>
-      <x:c r="B35" s="76" t="n">
-        <x:f>SUM(K35:Q35)</x:f>
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C35" s="78" t="str">
-        <x:v>Pokémon Red / Emerald</x:v>
-      </x:c>
-      <x:c r="D35" s="78" t="str">
-        <x:v>Continual-harness contrast</x:v>
-      </x:c>
-      <x:c r="E35" s="78" t="str">
-        <x:v>无重置对照</x:v>
-      </x:c>
-      <x:c r="F35" s="78" t="str">
-        <x:v>长程游戏模拟器</x:v>
-      </x:c>
-      <x:c r="G35" s="78" t="str">
-        <x:v>controller actions</x:v>
-      </x:c>
-      <x:c r="H35" s="78" t="str">
-        <x:v>不进入当前路线</x:v>
-      </x:c>
-      <x:c r="I35" s="78" t="str">
-        <x:v>里程碑/进度</x:v>
-      </x:c>
-      <x:c r="J35" s="78" t="str">
-        <x:v>刻意不重置</x:v>
-      </x:c>
-      <x:c r="K35" s="76" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L35" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M35" s="76" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N35" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O35" s="76" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P35" s="76" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q35" s="76" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R35" s="78" t="str">
-        <x:v>与本项目依赖可重置环境节点和父节点回测的设计冲突。</x:v>
-      </x:c>
-      <x:c r="S35" s="77" t="str">
+      <x:c r="B35" s="98" t="str">
+        <x:v>Pokemon Red / Emerald long-running agents</x:v>
+      </x:c>
+      <x:c r="C35" s="98" t="str">
+        <x:v>长时间、无频繁 reset 的游戏 Agent 实验，关注 harness、记忆和持续适应。它与本项目以可重置父子环境做因果比较的设计不同。</x:v>
+      </x:c>
+      <x:c r="D35" s="98" t="str">
+        <x:v>持续游戏存档、地图、队伍、物品和剧情进度；状态长期累积。</x:v>
+      </x:c>
+      <x:c r="E35" s="98" t="str">
+        <x:v>controller actions + 屏幕/内存观察。</x:v>
+      </x:c>
+      <x:c r="F35" s="98" t="str">
+        <x:v>Agent 连续运行数小时，探索地图、战斗、管理队伍并推进剧情，失败后不回到统一初始点。</x:v>
+      </x:c>
+      <x:c r="G35" s="98" t="str">
+        <x:v>剧情里程碑、区域进度或人工定义的长期指标。</x:v>
+      </x:c>
+      <x:c r="H35" s="98" t="str">
+        <x:v>可研究 f_O、Budget 和长期 Setup，但严格父节点回测与等价 reset 较难。</x:v>
+      </x:c>
+      <x:c r="I35" s="98" t="str">
+        <x:v>作为 continual harness 对照，提醒我们环境演化结果依赖可复现的初始状态和 verifier。</x:v>
+      </x:c>
+      <x:c r="J35" s="100" t="str">
+        <x:v>https://arxiv.org/abs/2605.09998</x:v>
+      </x:c>
+      <x:c r="K35" s="100" t="str">
+        <x:v>https://arxiv.org/abs/2605.09998</x:v>
+      </x:c>
+      <x:c r="L35" s="99" t="str">
+        <x:v>无重置持续适应对照</x:v>
+      </x:c>
+      <x:c r="M35" s="99" t="str">
         <x:v>S17</x:v>
       </x:c>
+      <x:c r="N35"/>
+      <x:c r="O35"/>
+      <x:c r="P35"/>
+      <x:c r="Q35"/>
+      <x:c r="R35"/>
+      <x:c r="S35"/>
     </x:row>
   </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="I4:M4"/>
+    <x:mergeCell ref="I5:M5"/>
+  </x:mergeCells>
   <x:conditionalFormatting sqref="A8:A33">
     <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="P0"/>
     <x:cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="P1"/>
@@ -2642,6 +2392,12 @@
     <x:cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="P0"/>
     <x:cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="P1"/>
     <x:cfRule type="containsText" dxfId="5" priority="6" operator="containsText" text="P2"/>
+    <x:cfRule type="containsText" dxfId="6" priority="8" operator="containsText" text="P0"/>
+    <x:cfRule type="containsText" dxfId="7" priority="9" operator="containsText" text="P1"/>
+    <x:cfRule type="containsText" dxfId="8" priority="10" operator="containsText" text="P2"/>
+    <x:cfRule type="containsText" dxfId="9" priority="11" operator="containsText" text="P0"/>
+    <x:cfRule type="containsText" dxfId="10" priority="12" operator="containsText" text="P1"/>
+    <x:cfRule type="containsText" dxfId="11" priority="13" operator="containsText" text="P2"/>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="B8:B35">
     <x:cfRule type="colorScale" priority="7">
@@ -2657,7 +2413,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R537da52262cb4d40"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb5e8d052db748cd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3068,7 +2824,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2e1640148434e84"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re0ac59b202744cb5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3769,7 +3525,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7527eac63be34721"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f729553efc9418b"/>
   </x:tableParts>
 </x:worksheet>
 </file>